--- a/data/laporan_keuangan.xlsx
+++ b/data/laporan_keuangan.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sandaranggas/Library/CloudStorage/GoogleDrive-admin@sandarangga.com/My Drive/Pribadi (1)/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB90E2D1-B951-0442-AE68-A87AF692E558}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DF47169-80B4-7A45-812E-74E4032F56A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -95,7 +95,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="713">
   <si>
     <t>NO</t>
   </si>
@@ -2225,6 +2225,15 @@
   </si>
   <si>
     <t>Penghitungan Kotak Amal 14 Juni 2026</t>
+  </si>
+  <si>
+    <t>Gaji Bang Zaini Bulan Juni</t>
+  </si>
+  <si>
+    <t>infaq khotib jum'at</t>
+  </si>
+  <si>
+    <t>Token Listrik 500 Ribu</t>
   </si>
 </sst>
 </file>
@@ -2999,10 +3008,10 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -17627,9 +17636,6 @@
         <f t="shared" si="21"/>
         <v>9228600</v>
       </c>
-      <c r="H629">
-        <v>1446000</v>
-      </c>
     </row>
     <row r="630" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A630" s="19">
@@ -17649,9 +17655,6 @@
         <f t="shared" si="21"/>
         <v>9028600</v>
       </c>
-      <c r="H630">
-        <v>800000</v>
-      </c>
     </row>
     <row r="631" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A631" s="19">
@@ -17671,10 +17674,7 @@
         <f t="shared" si="21"/>
         <v>6968600</v>
       </c>
-      <c r="H631" s="67">
-        <f>H629-H630</f>
-        <v>646000</v>
-      </c>
+      <c r="H631" s="67"/>
     </row>
     <row r="632" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A632" s="19">
@@ -17693,9 +17693,6 @@
       <c r="F632" s="32">
         <f t="shared" si="21"/>
         <v>6818600</v>
-      </c>
-      <c r="H632">
-        <v>500000</v>
       </c>
     </row>
     <row r="633" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
@@ -17716,10 +17713,7 @@
         <f t="shared" si="21"/>
         <v>7318600</v>
       </c>
-      <c r="H633" s="67">
-        <f>H631-H632</f>
-        <v>146000</v>
-      </c>
+      <c r="H633" s="67"/>
     </row>
     <row r="634" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A634" s="19">
@@ -18080,7 +18074,7 @@
       </c>
       <c r="E652" s="37"/>
       <c r="F652" s="79">
-        <f t="shared" ref="F652:F684" si="23">F651+D652-E652</f>
+        <f t="shared" ref="F652:F690" si="23">F651+D652-E652</f>
         <v>8218600</v>
       </c>
     </row>
@@ -18698,161 +18692,232 @@
       <c r="A685" s="19">
         <v>633</v>
       </c>
-      <c r="B685" s="68"/>
-      <c r="C685" s="36"/>
+      <c r="B685" s="68">
+        <v>46198</v>
+      </c>
+      <c r="C685" s="36" t="s">
+        <v>710</v>
+      </c>
       <c r="D685" s="37"/>
-      <c r="E685" s="37"/>
-      <c r="F685" s="79"/>
+      <c r="E685" s="37">
+        <v>600000</v>
+      </c>
+      <c r="F685" s="79">
+        <f t="shared" si="23"/>
+        <v>17442601</v>
+      </c>
     </row>
     <row r="686" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A686" s="19">
         <v>634</v>
       </c>
-      <c r="B686" s="68"/>
-      <c r="C686" s="36"/>
+      <c r="B686" s="68">
+        <v>46199</v>
+      </c>
+      <c r="C686" s="36" t="s">
+        <v>711</v>
+      </c>
       <c r="D686" s="37"/>
-      <c r="E686" s="37"/>
-      <c r="F686" s="79"/>
+      <c r="E686" s="37">
+        <v>500000</v>
+      </c>
+      <c r="F686" s="79">
+        <f t="shared" si="23"/>
+        <v>16942601</v>
+      </c>
     </row>
     <row r="687" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A687" s="19"/>
-      <c r="B687" s="81"/>
-      <c r="C687" s="80" t="s">
+      <c r="A687" s="19">
+        <v>635</v>
+      </c>
+      <c r="B687" s="68">
+        <v>46204</v>
+      </c>
+      <c r="C687" s="36" t="s">
+        <v>712</v>
+      </c>
+      <c r="D687" s="37"/>
+      <c r="E687" s="37">
+        <v>500000</v>
+      </c>
+      <c r="F687" s="79">
+        <f t="shared" si="23"/>
+        <v>16442601</v>
+      </c>
+    </row>
+    <row r="688" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A688" s="19">
+        <v>636</v>
+      </c>
+      <c r="B688" s="68">
+        <v>46213</v>
+      </c>
+      <c r="C688" s="36" t="s">
+        <v>712</v>
+      </c>
+      <c r="D688" s="37"/>
+      <c r="E688" s="37">
+        <v>500000</v>
+      </c>
+      <c r="F688" s="79">
+        <f t="shared" si="23"/>
+        <v>15942601</v>
+      </c>
+    </row>
+    <row r="689" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A689" s="19">
+        <v>637</v>
+      </c>
+      <c r="B689" s="68">
+        <v>46220</v>
+      </c>
+      <c r="C689" s="36" t="s">
+        <v>426</v>
+      </c>
+      <c r="D689" s="37"/>
+      <c r="E689" s="37">
+        <v>500000</v>
+      </c>
+      <c r="F689" s="79">
+        <f t="shared" si="23"/>
+        <v>15442601</v>
+      </c>
+      <c r="H689" s="67"/>
+    </row>
+    <row r="690" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A690" s="19">
+        <v>638</v>
+      </c>
+      <c r="B690" s="68">
+        <v>46221</v>
+      </c>
+      <c r="C690" s="36" t="s">
+        <v>708</v>
+      </c>
+      <c r="D690" s="37">
+        <v>300000</v>
+      </c>
+      <c r="E690" s="37"/>
+      <c r="F690" s="79">
+        <f t="shared" si="23"/>
+        <v>15742601</v>
+      </c>
+    </row>
+    <row r="691" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A691" s="19">
+        <v>639</v>
+      </c>
+      <c r="B691" s="68"/>
+      <c r="C691" s="36"/>
+      <c r="D691" s="37"/>
+      <c r="E691" s="37"/>
+      <c r="F691" s="79"/>
+    </row>
+    <row r="692" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A692" s="19">
+        <v>640</v>
+      </c>
+      <c r="B692" s="68"/>
+      <c r="C692" s="36"/>
+      <c r="D692" s="37"/>
+      <c r="E692" s="37"/>
+      <c r="F692" s="79"/>
+    </row>
+    <row r="693" spans="1:8" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A693" s="19"/>
+      <c r="B693" s="81"/>
+      <c r="C693" s="80" t="s">
         <v>191</v>
       </c>
-      <c r="D687" s="74"/>
-      <c r="E687" s="74"/>
-      <c r="F687" s="78">
-        <f>F684</f>
-        <v>18042601</v>
-      </c>
-    </row>
-    <row r="688" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B688" s="1"/>
-      <c r="C688" s="1"/>
-      <c r="D688" s="1"/>
-      <c r="E688" s="1"/>
-      <c r="F688" s="1"/>
-    </row>
-    <row r="689" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B689" s="1"/>
-      <c r="C689" s="1"/>
-      <c r="D689" s="1"/>
-      <c r="E689" s="23" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="690" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B690" s="91" t="s">
-        <v>192</v>
-      </c>
-      <c r="C690" s="89"/>
-      <c r="D690" s="1"/>
-      <c r="E690" s="1"/>
-      <c r="F690" s="1"/>
-    </row>
-    <row r="691" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B691" s="23"/>
-      <c r="C691" s="1"/>
-      <c r="D691" s="1"/>
-    </row>
-    <row r="692" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B692" s="22" t="s">
-        <v>193</v>
-      </c>
-      <c r="C692" s="1"/>
-      <c r="D692" s="1"/>
-      <c r="E692" s="23" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="693" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B693" s="23"/>
-      <c r="C693" s="1"/>
-      <c r="D693" s="1"/>
-      <c r="E693" s="1"/>
-      <c r="F693" s="1"/>
-    </row>
-    <row r="694" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D693" s="74"/>
+      <c r="E693" s="74"/>
+      <c r="F693" s="78">
+        <f>F690</f>
+        <v>15742601</v>
+      </c>
+    </row>
+    <row r="694" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B694" s="1"/>
       <c r="C694" s="1"/>
       <c r="D694" s="1"/>
       <c r="E694" s="1"/>
       <c r="F694" s="1"/>
     </row>
-    <row r="695" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B695" s="1" t="s">
-        <v>195</v>
-      </c>
+    <row r="695" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B695" s="1"/>
       <c r="C695" s="1"/>
       <c r="D695" s="1"/>
       <c r="E695" s="23" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="696" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B696" s="1"/>
-      <c r="C696" s="1"/>
+        <v>656</v>
+      </c>
+    </row>
+    <row r="696" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B696" s="91" t="s">
+        <v>192</v>
+      </c>
+      <c r="C696" s="89"/>
       <c r="D696" s="1"/>
       <c r="E696" s="1"/>
       <c r="F696" s="1"/>
     </row>
-    <row r="697" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="697" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B697" s="23"/>
       <c r="C697" s="1"/>
       <c r="D697" s="1"/>
-      <c r="E697">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="698" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B698" s="1"/>
+    </row>
+    <row r="698" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B698" s="22" t="s">
+        <v>193</v>
+      </c>
       <c r="C698" s="1"/>
       <c r="D698" s="1"/>
-    </row>
-    <row r="699" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B699" s="1"/>
+      <c r="E698" s="23" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="699" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B699" s="23"/>
       <c r="C699" s="1"/>
       <c r="D699" s="1"/>
       <c r="E699" s="1"/>
       <c r="F699" s="1"/>
     </row>
-    <row r="700" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="700" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B700" s="1"/>
       <c r="C700" s="1"/>
       <c r="D700" s="1"/>
       <c r="E700" s="1"/>
       <c r="F700" s="1"/>
     </row>
-    <row r="701" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B701" s="24" t="s">
-        <v>197</v>
+    <row r="701" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B701" s="1" t="s">
+        <v>195</v>
       </c>
       <c r="C701" s="1"/>
       <c r="D701" s="1"/>
-      <c r="E701" s="1"/>
-      <c r="F701" s="1"/>
-    </row>
-    <row r="702" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E701" s="23" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="702" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B702" s="1"/>
       <c r="C702" s="1"/>
       <c r="D702" s="1"/>
       <c r="E702" s="1"/>
       <c r="F702" s="1"/>
     </row>
-    <row r="703" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B703" s="1"/>
+    <row r="703" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B703" s="23"/>
       <c r="C703" s="1"/>
       <c r="D703" s="1"/>
-      <c r="E703" s="1"/>
-      <c r="F703" s="1"/>
-    </row>
-    <row r="704" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="E703">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="704" spans="1:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B704" s="1"/>
       <c r="C704" s="1"/>
       <c r="D704" s="1"/>
-      <c r="E704" s="1"/>
-      <c r="F704" s="1"/>
     </row>
     <row r="705" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B705" s="1"/>
@@ -18869,7 +18934,9 @@
       <c r="F706" s="1"/>
     </row>
     <row r="707" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B707" s="1"/>
+      <c r="B707" s="24" t="s">
+        <v>197</v>
+      </c>
       <c r="C707" s="1"/>
       <c r="D707" s="1"/>
       <c r="E707" s="1"/>
@@ -19218,12 +19285,48 @@
       <c r="E756" s="1"/>
       <c r="F756" s="1"/>
     </row>
-    <row r="757" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="757" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B757" s="1"/>
+      <c r="C757" s="1"/>
+      <c r="D757" s="1"/>
+      <c r="E757" s="1"/>
+      <c r="F757" s="1"/>
+    </row>
+    <row r="758" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B758" s="1"/>
+      <c r="C758" s="1"/>
+      <c r="D758" s="1"/>
+      <c r="E758" s="1"/>
+      <c r="F758" s="1"/>
+    </row>
+    <row r="759" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B759" s="1"/>
+      <c r="C759" s="1"/>
+      <c r="D759" s="1"/>
+      <c r="E759" s="1"/>
+      <c r="F759" s="1"/>
+    </row>
+    <row r="760" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B760" s="1"/>
+      <c r="C760" s="1"/>
+      <c r="D760" s="1"/>
+      <c r="E760" s="1"/>
+      <c r="F760" s="1"/>
+    </row>
+    <row r="761" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B761" s="1"/>
+      <c r="C761" s="1"/>
+      <c r="D761" s="1"/>
+      <c r="E761" s="1"/>
+      <c r="F761" s="1"/>
+    </row>
+    <row r="762" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B762" s="1"/>
+      <c r="C762" s="1"/>
+      <c r="D762" s="1"/>
+      <c r="E762" s="1"/>
+      <c r="F762" s="1"/>
+    </row>
     <row r="763" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="764" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="765" spans="2:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -19487,10 +19590,10 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="B690:C690"/>
+    <mergeCell ref="B696:C696"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="B134:B686">
+  <conditionalFormatting sqref="B134:B692">
     <cfRule type="timePeriod" dxfId="5" priority="3" timePeriod="today">
       <formula>FLOOR(B134,1)=TODAY()</formula>
     </cfRule>
@@ -19526,11 +19629,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="86" t="s">
         <v>460</v>
       </c>
-      <c r="B1" s="87"/>
-      <c r="C1" s="87"/>
+      <c r="B1" s="86"/>
+      <c r="C1" s="86"/>
     </row>
     <row r="2" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
@@ -19702,11 +19805,11 @@
       </c>
     </row>
     <row r="18" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="87" t="s">
+      <c r="A18" s="86" t="s">
         <v>486</v>
       </c>
-      <c r="B18" s="87"/>
-      <c r="C18" s="87"/>
+      <c r="B18" s="86"/>
+      <c r="C18" s="86"/>
     </row>
     <row r="19" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="48">
@@ -19751,11 +19854,11 @@
       </c>
     </row>
     <row r="23" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="87" t="s">
+      <c r="A23" s="86" t="s">
         <v>498</v>
       </c>
-      <c r="B23" s="87"/>
-      <c r="C23" s="87"/>
+      <c r="B23" s="86"/>
+      <c r="C23" s="86"/>
     </row>
     <row r="24" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="48">
@@ -19849,11 +19952,11 @@
     </row>
     <row r="32" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="33" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="87" t="s">
+      <c r="A33" s="86" t="s">
         <v>499</v>
       </c>
-      <c r="B33" s="87"/>
-      <c r="C33" s="87"/>
+      <c r="B33" s="86"/>
+      <c r="C33" s="86"/>
     </row>
     <row r="34" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="48">
@@ -19946,11 +20049,11 @@
       </c>
     </row>
     <row r="42" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="87" t="s">
+      <c r="A42" s="86" t="s">
         <v>504</v>
       </c>
-      <c r="B42" s="87"/>
-      <c r="C42" s="87"/>
+      <c r="B42" s="86"/>
+      <c r="C42" s="86"/>
     </row>
     <row r="43" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="48">
@@ -20044,11 +20147,11 @@
     </row>
     <row r="51" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="52" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="87" t="s">
+      <c r="A52" s="86" t="s">
         <v>507</v>
       </c>
-      <c r="B52" s="87"/>
-      <c r="C52" s="87"/>
+      <c r="B52" s="86"/>
+      <c r="C52" s="86"/>
     </row>
     <row r="53" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="48">
@@ -20142,11 +20245,11 @@
     </row>
     <row r="61" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="62" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="87" t="s">
+      <c r="A62" s="86" t="s">
         <v>513</v>
       </c>
-      <c r="B62" s="87"/>
-      <c r="C62" s="87"/>
+      <c r="B62" s="86"/>
+      <c r="C62" s="86"/>
     </row>
     <row r="63" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="48">
@@ -20241,11 +20344,11 @@
     <row r="71" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="72" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="73" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="87" t="s">
+      <c r="A73" s="86" t="s">
         <v>526</v>
       </c>
-      <c r="B73" s="87"/>
-      <c r="C73" s="87"/>
+      <c r="B73" s="86"/>
+      <c r="C73" s="86"/>
     </row>
     <row r="74" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="48">
@@ -20352,11 +20455,11 @@
     <row r="83" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="84" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="85" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="87" t="s">
+      <c r="A85" s="86" t="s">
         <v>535</v>
       </c>
-      <c r="B85" s="87"/>
-      <c r="C85" s="87"/>
+      <c r="B85" s="86"/>
+      <c r="C85" s="86"/>
     </row>
     <row r="86" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A86" s="48">
@@ -20446,11 +20549,11 @@
     </row>
     <row r="95" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="96" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="87" t="s">
+      <c r="A96" s="86" t="s">
         <v>541</v>
       </c>
-      <c r="B96" s="87"/>
-      <c r="C96" s="87"/>
+      <c r="B96" s="86"/>
+      <c r="C96" s="86"/>
     </row>
     <row r="97" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A97" s="48">
@@ -20548,11 +20651,11 @@
     </row>
     <row r="106" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="107" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="87" t="s">
+      <c r="A107" s="86" t="s">
         <v>542</v>
       </c>
-      <c r="B107" s="87"/>
-      <c r="C107" s="87"/>
+      <c r="B107" s="86"/>
+      <c r="C107" s="86"/>
     </row>
     <row r="108" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A108" s="48">
@@ -20650,11 +20753,11 @@
     </row>
     <row r="117" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="118" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="87" t="s">
+      <c r="A118" s="86" t="s">
         <v>543</v>
       </c>
-      <c r="B118" s="87"/>
-      <c r="C118" s="87"/>
+      <c r="B118" s="86"/>
+      <c r="C118" s="86"/>
     </row>
     <row r="119" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="48">
@@ -20752,11 +20855,11 @@
     </row>
     <row r="128" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="129" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A129" s="86" t="s">
+      <c r="A129" s="87" t="s">
         <v>555</v>
       </c>
-      <c r="B129" s="87"/>
-      <c r="C129" s="87"/>
+      <c r="B129" s="86"/>
+      <c r="C129" s="86"/>
     </row>
     <row r="130" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A130" s="48">
@@ -20854,11 +20957,11 @@
     </row>
     <row r="139" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="140" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="86" t="s">
+      <c r="A140" s="87" t="s">
         <v>556</v>
       </c>
-      <c r="B140" s="87"/>
-      <c r="C140" s="87"/>
+      <c r="B140" s="86"/>
+      <c r="C140" s="86"/>
     </row>
     <row r="141" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A141" s="48">
@@ -20956,11 +21059,11 @@
     </row>
     <row r="150" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="151" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="86" t="s">
+      <c r="A151" s="87" t="s">
         <v>562</v>
       </c>
-      <c r="B151" s="87"/>
-      <c r="C151" s="87"/>
+      <c r="B151" s="86"/>
+      <c r="C151" s="86"/>
     </row>
     <row r="152" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A152" s="48">
@@ -21058,11 +21161,11 @@
     </row>
     <row r="161" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="162" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="86" t="s">
+      <c r="A162" s="87" t="s">
         <v>572</v>
       </c>
-      <c r="B162" s="87"/>
-      <c r="C162" s="87"/>
+      <c r="B162" s="86"/>
+      <c r="C162" s="86"/>
     </row>
     <row r="163" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A163" s="48">
@@ -21160,11 +21263,11 @@
     </row>
     <row r="172" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="173" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="86" t="s">
+      <c r="A173" s="87" t="s">
         <v>573</v>
       </c>
-      <c r="B173" s="87"/>
-      <c r="C173" s="87"/>
+      <c r="B173" s="86"/>
+      <c r="C173" s="86"/>
     </row>
     <row r="174" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="48">
@@ -23404,20 +23507,6 @@
     <row r="1000" ht="14.25" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="30">
-    <mergeCell ref="A275:C275"/>
-    <mergeCell ref="A228:C228"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A33:C33"/>
-    <mergeCell ref="A42:C42"/>
-    <mergeCell ref="A73:C73"/>
-    <mergeCell ref="A52:C52"/>
-    <mergeCell ref="A62:C62"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A96:C96"/>
-    <mergeCell ref="A85:C85"/>
     <mergeCell ref="A333:C333"/>
     <mergeCell ref="A173:C173"/>
     <mergeCell ref="A151:C151"/>
@@ -23434,6 +23523,20 @@
     <mergeCell ref="A206:C206"/>
     <mergeCell ref="A309:C309"/>
     <mergeCell ref="A286:C286"/>
+    <mergeCell ref="A275:C275"/>
+    <mergeCell ref="A228:C228"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A18:C18"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A33:C33"/>
+    <mergeCell ref="A42:C42"/>
+    <mergeCell ref="A73:C73"/>
+    <mergeCell ref="A52:C52"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A96:C96"/>
+    <mergeCell ref="A85:C85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>

--- a/data/laporan_keuangan.xlsx
+++ b/data/laporan_keuangan.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G685"/>
+  <dimension ref="A1:G686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -12236,56 +12236,56 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B438" s="2" t="n">
         <v>45353</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Sumbangan Hamba Allah</t>
+          <t>Infaq untuk Ustadz Tarhib Ramadhan</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E438" s="3" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F438" s="3" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="G438" s="3" t="n">
-        <v>5119290</v>
+        <v>3619290</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B439" s="2" t="n">
         <v>45353</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Infaq untuk Ustadz Tarhib Ramadhan</t>
+          <t>Sumbangan Hamba Allah</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E439" s="3" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="F439" s="3" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="G439" s="3" t="n">
-        <v>3619290</v>
+        <v>5119290</v>
       </c>
     </row>
     <row r="440">
@@ -15125,56 +15125,56 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B545" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Reimburse Infaq Khotib Jum'at 25 April 2025</t>
+          <t>Pembelian Token Listrik</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Listrik &amp; Perawatan</t>
         </is>
       </c>
       <c r="E545" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F545" s="3" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="G545" s="3" t="n">
-        <v>5223000</v>
+        <v>4223000</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B546" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Pembelian Token Listrik</t>
+          <t>Reimburse Infaq Khotib Jum'at 25 April 2025</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Listrik &amp; Perawatan</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E546" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F546" s="3" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="G546" s="3" t="n">
-        <v>4223000</v>
+        <v>5223000</v>
       </c>
     </row>
     <row r="547">
@@ -15422,56 +15422,56 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B556" s="2" t="n">
         <v>45802</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan Mei</t>
+          <t>infaq dari Jamaah via transfer dan QRIS</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E556" s="3" t="n">
-        <v>0</v>
+        <v>1370500</v>
       </c>
       <c r="F556" s="3" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="G556" s="3" t="n">
-        <v>6577600</v>
+        <v>7948100</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B557" s="2" t="n">
         <v>45802</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>infaq dari Jamaah via transfer dan QRIS</t>
+          <t>Gaji Bang Zaeni Bulan Mei</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E557" s="3" t="n">
-        <v>1370500</v>
+        <v>0</v>
       </c>
       <c r="F557" s="3" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="G557" s="3" t="n">
-        <v>7948100</v>
+        <v>6577600</v>
       </c>
     </row>
     <row r="558">
@@ -15719,83 +15719,83 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B567" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Juni 2025</t>
+          <t>infaq dari Jamaah via transfer dan QRIS</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E567" s="3" t="n">
-        <v>0</v>
+        <v>255000</v>
       </c>
       <c r="F567" s="3" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="G567" s="3" t="n">
-        <v>4540100</v>
+        <v>6656100</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B568" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Setoran Pembukaan Kotak Amal 30 Juni 2025</t>
+          <t>Subsidi TPA Bulan Juni 2025</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E568" s="3" t="n">
-        <v>1861000</v>
+        <v>0</v>
       </c>
       <c r="F568" s="3" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="G568" s="3" t="n">
-        <v>6401100</v>
+        <v>4540100</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B569" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>infaq dari Jamaah via transfer dan QRIS</t>
+          <t>Setoran Pembukaan Kotak Amal 30 Juni 2025</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E569" s="3" t="n">
-        <v>255000</v>
+        <v>1861000</v>
       </c>
       <c r="F569" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G569" s="3" t="n">
-        <v>6656100</v>
+        <v>6401100</v>
       </c>
     </row>
     <row r="570">
@@ -17312,41 +17312,41 @@
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B626" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Realisasi Pengajuan Majelis Ta'lim</t>
+          <t>Rekapan Infaq di rekening / QRIS</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Majelis Ta'lim</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E626" s="3" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F626" s="3" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G626" s="3" t="n">
-        <v>5618600</v>
+        <v>5918600</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="B627" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Dana Kegiatan TPA Al Ikhlas</t>
+          <t>Subsidi TPA Bulan Januari 2026</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -17361,61 +17361,61 @@
         <v>1200000</v>
       </c>
       <c r="G627" s="3" t="n">
-        <v>6118600</v>
+        <v>4718600</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="B628" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Rekapan Infaq di rekening / QRIS</t>
+          <t>Dana Kegiatan TPA Al Ikhlas</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E628" s="3" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="F628" s="3" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="G628" s="3" t="n">
-        <v>5918600</v>
+        <v>6118600</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="B629" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Januari 2026</t>
+          <t>Realisasi Pengajuan Majelis Ta'lim</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Majelis Ta'lim</t>
         </is>
       </c>
       <c r="E629" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F629" s="3" t="n">
-        <v>1200000</v>
+        <v>500000</v>
       </c>
       <c r="G629" s="3" t="n">
-        <v>4718600</v>
+        <v>5618600</v>
       </c>
     </row>
     <row r="630">
@@ -17663,56 +17663,56 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B639" s="2" t="n">
         <v>46074</v>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Sumbangan Kantor Pak Jalal</t>
+          <t>Infaq Imam dan Ceramah Tarawih</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E639" s="3" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="F639" s="3" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="G639" s="3" t="n">
-        <v>11318600</v>
+        <v>9818600</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="B640" s="2" t="n">
         <v>46074</v>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Infaq Imam dan Ceramah Tarawih</t>
+          <t>Sumbangan Kantor Pak Jalal</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E640" s="3" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="F640" s="3" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="G640" s="3" t="n">
-        <v>9818600</v>
+        <v>11318600</v>
       </c>
     </row>
     <row r="641">
@@ -17987,56 +17987,56 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B651" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Maret 2026</t>
+          <t>Rekapan Infaq di rekening / QRIS per 13 Maret 2026</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E651" s="3" t="n">
-        <v>0</v>
+        <v>1982000</v>
       </c>
       <c r="F651" s="3" t="n">
-        <v>1100000</v>
+        <v>0</v>
       </c>
       <c r="G651" s="3" t="n">
-        <v>8896600</v>
+        <v>10878600</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B652" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Rekapan Infaq di rekening / QRIS per 13 Maret 2026</t>
+          <t>Subsidi TPA Bulan Maret 2026</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>1982000</v>
+        <v>0</v>
       </c>
       <c r="F652" s="3" t="n">
-        <v>0</v>
+        <v>1100000</v>
       </c>
       <c r="G652" s="3" t="n">
-        <v>10878600</v>
+        <v>8896600</v>
       </c>
     </row>
     <row r="653">
@@ -18284,56 +18284,56 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B662" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Infaq Khotib Jum'at</t>
+          <t>Gaji Bang Zaeini Bulan April</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E662" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F662" s="3" t="n">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="G662" s="3" t="n">
-        <v>10191600</v>
+        <v>9591600</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B663" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeini Bulan April</t>
+          <t>Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E663" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F663" s="3" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="G663" s="3" t="n">
-        <v>9591600</v>
+        <v>10191600</v>
       </c>
     </row>
     <row r="664">
@@ -18500,110 +18500,110 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B670" s="2" t="n">
         <v>46172</v>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Tambahan Infaq Ustadz untuk acara remaja masjid</t>
+          <t>Subsidi TPA Bulan Mei 2026</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E670" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F670" s="3" t="n">
-        <v>300000</v>
+        <v>800000</v>
       </c>
       <c r="G670" s="3" t="n">
-        <v>7891600</v>
+        <v>7091600</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B671" s="2" t="n">
         <v>46172</v>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Mei 2026</t>
+          <t>Tambahan Infaq Ustadz untuk acara remaja masjid</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E671" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F671" s="3" t="n">
-        <v>800000</v>
+        <v>300000</v>
       </c>
       <c r="G671" s="3" t="n">
-        <v>7091600</v>
+        <v>7891600</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B672" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Penghitungan Kotak Amal 21 Mei 2026</t>
+          <t>Rekapan Infaq di rekening / QRIS/</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>2115000</v>
+        <v>4658001</v>
       </c>
       <c r="F672" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G672" s="3" t="n">
-        <v>9206600</v>
+        <v>13864601</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B673" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Rekapan Infaq di rekening / QRIS/</t>
+          <t>Penghitungan Kotak Amal 21 Mei 2026</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>4658001</v>
+        <v>2115000</v>
       </c>
       <c r="F673" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G673" s="3" t="n">
-        <v>13864601</v>
+        <v>9206600</v>
       </c>
     </row>
     <row r="674">
@@ -18904,15 +18904,42 @@
       </c>
     </row>
     <row r="685">
-      <c r="C685" s="4" t="inlineStr">
+      <c r="A685" t="n">
+        <v>641</v>
+      </c>
+      <c r="B685" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Pemasukan Kotak Amal</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Kotak Amal / Kencleng</t>
+        </is>
+      </c>
+      <c r="E685" s="3" t="n">
+        <v>3108000</v>
+      </c>
+      <c r="F685" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G685" s="3" t="n">
+        <v>18819934</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="C686" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E685" s="5" t="n">
-        <v>378166644</v>
-      </c>
-      <c r="F685" s="5" t="n">
+      <c r="E686" s="5" t="n">
+        <v>381274644</v>
+      </c>
+      <c r="F686" s="5" t="n">
         <v>360617210</v>
       </c>
     </row>

--- a/data/laporan_keuangan.xlsx
+++ b/data/laporan_keuangan.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G686"/>
+  <dimension ref="A1:G684"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9617,56 +9617,56 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B341" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan April 2023</t>
+          <t>Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E341" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F341" s="3" t="n">
-        <v>600000</v>
+        <v>300000</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>12049390</v>
+        <v>12649390</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B342" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Infaq Khotib Jum'at</t>
+          <t>Gaji Bang Zaeni Bulan April 2023</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E342" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>300000</v>
+        <v>600000</v>
       </c>
       <c r="G342" s="3" t="n">
-        <v>12649390</v>
+        <v>12049390</v>
       </c>
     </row>
     <row r="343">
@@ -12236,56 +12236,56 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B438" s="2" t="n">
         <v>45353</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Infaq untuk Ustadz Tarhib Ramadhan</t>
+          <t>Sumbangan Hamba Allah</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E438" s="3" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="F438" s="3" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="G438" s="3" t="n">
-        <v>3619290</v>
+        <v>5119290</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B439" s="2" t="n">
         <v>45353</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Sumbangan Hamba Allah</t>
+          <t>Infaq untuk Ustadz Tarhib Ramadhan</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E439" s="3" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F439" s="3" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="G439" s="3" t="n">
-        <v>5119290</v>
+        <v>3619290</v>
       </c>
     </row>
     <row r="440">
@@ -15125,56 +15125,56 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B545" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Pembelian Token Listrik</t>
+          <t>Reimburse Infaq Khotib Jum'at 25 April 2025</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Listrik &amp; Perawatan</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E545" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F545" s="3" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="G545" s="3" t="n">
-        <v>4223000</v>
+        <v>5223000</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B546" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Reimburse Infaq Khotib Jum'at 25 April 2025</t>
+          <t>Pembelian Token Listrik</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Listrik &amp; Perawatan</t>
         </is>
       </c>
       <c r="E546" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F546" s="3" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="G546" s="3" t="n">
-        <v>5223000</v>
+        <v>4223000</v>
       </c>
     </row>
     <row r="547">
@@ -15422,56 +15422,56 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B556" s="2" t="n">
         <v>45802</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>infaq dari Jamaah via transfer dan QRIS</t>
+          <t>Gaji Bang Zaeni Bulan Mei</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E556" s="3" t="n">
-        <v>1370500</v>
+        <v>0</v>
       </c>
       <c r="F556" s="3" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="G556" s="3" t="n">
-        <v>7948100</v>
+        <v>6577600</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B557" s="2" t="n">
         <v>45802</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan Mei</t>
+          <t>infaq dari Jamaah via transfer dan QRIS</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E557" s="3" t="n">
-        <v>0</v>
+        <v>1370500</v>
       </c>
       <c r="F557" s="3" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="G557" s="3" t="n">
-        <v>6577600</v>
+        <v>7948100</v>
       </c>
     </row>
     <row r="558">
@@ -15719,83 +15719,83 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="B567" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>infaq dari Jamaah via transfer dan QRIS</t>
+          <t>Subsidi TPA Bulan Juni 2025</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E567" s="3" t="n">
-        <v>255000</v>
+        <v>0</v>
       </c>
       <c r="F567" s="3" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="G567" s="3" t="n">
-        <v>6656100</v>
+        <v>4540100</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B568" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Juni 2025</t>
+          <t>Setoran Pembukaan Kotak Amal 30 Juni 2025</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E568" s="3" t="n">
-        <v>0</v>
+        <v>1861000</v>
       </c>
       <c r="F568" s="3" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="G568" s="3" t="n">
-        <v>4540100</v>
+        <v>6401100</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B569" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Setoran Pembukaan Kotak Amal 30 Juni 2025</t>
+          <t>infaq dari Jamaah via transfer dan QRIS</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E569" s="3" t="n">
-        <v>1861000</v>
+        <v>255000</v>
       </c>
       <c r="F569" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G569" s="3" t="n">
-        <v>6401100</v>
+        <v>6656100</v>
       </c>
     </row>
     <row r="570">
@@ -18863,7 +18863,7 @@
       </c>
       <c r="D683" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E683" s="3" t="n">
@@ -18877,69 +18877,15 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" t="n">
-        <v>640</v>
-      </c>
-      <c r="B684" s="2" t="n">
-        <v>46228</v>
-      </c>
-      <c r="C684" t="inlineStr">
-        <is>
-          <t>Pemasukan rekening/qris</t>
-        </is>
-      </c>
-      <c r="D684" t="inlineStr">
-        <is>
-          <t>Infaq Rekening/QRIS</t>
-        </is>
-      </c>
-      <c r="E684" s="3" t="n">
-        <v>569333</v>
-      </c>
-      <c r="F684" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G684" s="3" t="n">
-        <v>15711934</v>
-      </c>
-    </row>
-    <row r="685">
-      <c r="A685" t="n">
-        <v>641</v>
-      </c>
-      <c r="B685" s="2" t="n">
-        <v>46230</v>
-      </c>
-      <c r="C685" t="inlineStr">
-        <is>
-          <t>Pemasukan Kotak Amal</t>
-        </is>
-      </c>
-      <c r="D685" t="inlineStr">
-        <is>
-          <t>Kotak Amal / Kencleng</t>
-        </is>
-      </c>
-      <c r="E685" s="3" t="n">
-        <v>3108000</v>
-      </c>
-      <c r="F685" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G685" s="3" t="n">
-        <v>18819934</v>
-      </c>
-    </row>
-    <row r="686">
-      <c r="C686" s="4" t="inlineStr">
+      <c r="C684" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E686" s="5" t="n">
-        <v>381274644</v>
-      </c>
-      <c r="F686" s="5" t="n">
+      <c r="E684" s="5" t="n">
+        <v>377597311</v>
+      </c>
+      <c r="F684" s="5" t="n">
         <v>360617210</v>
       </c>
     </row>

--- a/data/laporan_keuangan.xlsx
+++ b/data/laporan_keuangan.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G684"/>
+  <dimension ref="A1:G685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1001,29 +1001,29 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B21" s="2" t="n">
         <v>43595</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Penyaluran dana ke Majelis Ta'lim</t>
+          <t>Infaq Transport Ustadz Tarawih</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Majelis Ta'lim</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1200000</v>
+        <v>400000</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>3979200</v>
+        <v>3229200</v>
       </c>
     </row>
     <row r="22">
@@ -1055,29 +1055,29 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B23" s="2" t="n">
         <v>43595</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Infaq Transport Ustadz Tarawih</t>
+          <t>Penyaluran dana ke Majelis Ta'lim</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Majelis Ta'lim</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>400000</v>
+        <v>1200000</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3229200</v>
+        <v>3979200</v>
       </c>
     </row>
     <row r="24">
@@ -1865,56 +1865,56 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B53" s="2" t="n">
         <v>43723</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Infaq Pembicara untuk acara Muharram</t>
+          <t>Penyaluran dana ke Majelis Ta'lim</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Majelis Ta'lim</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1500000</v>
+        <v>1200000</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>2956890</v>
+        <v>1756890</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B54" s="2" t="n">
         <v>43723</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Penyaluran dana ke Majelis Ta'lim</t>
+          <t>Infaq Pembicara untuk acara Muharram</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Majelis Ta'lim</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1756890</v>
+        <v>2956890</v>
       </c>
     </row>
     <row r="55">
@@ -2135,29 +2135,29 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B63" s="2" t="n">
         <v>43792</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sumbangan dari RT 1 untuk Acara Maulid</t>
+          <t>Snack Anak2 untuk Acara Maulid</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Kegiatan &amp; Sosial</t>
+          <t>Konsumsi &amp; Kegiatan</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
         <v>300000</v>
       </c>
-      <c r="F63" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G63" s="3" t="n">
-        <v>4506890</v>
+        <v>3206890</v>
       </c>
     </row>
     <row r="64">
@@ -2189,29 +2189,29 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B65" s="2" t="n">
         <v>43792</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Snack Anak2 untuk Acara Maulid</t>
+          <t>Sumbangan dari RT 1 untuk Acara Maulid</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Konsumsi &amp; Kegiatan</t>
+          <t>Kegiatan &amp; Sosial</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>3206890</v>
+        <v>4506890</v>
       </c>
     </row>
     <row r="66">
@@ -2405,14 +2405,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B73" s="2" t="n">
         <v>43908</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Hardian</t>
+          <t>Infaq dari Pak Jalal</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2421,25 +2421,25 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="F73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>656890</v>
+        <v>756890</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B74" s="2" t="n">
         <v>43908</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Ridho</t>
+          <t>Infaq dari Pak Heri S</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2454,19 +2454,19 @@
         <v>0</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>606890</v>
+        <v>856890</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B75" s="2" t="n">
         <v>43908</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Heri S</t>
+          <t>Infaq dari Pak Hardian</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>856890</v>
+        <v>656890</v>
       </c>
     </row>
     <row r="76">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Jalal</t>
+          <t>Infaq dari Pak Ridho</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2508,12 +2508,12 @@
         <v>0</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>756890</v>
+        <v>606890</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B77" s="2" t="n">
         <v>43915</v>
@@ -2540,7 +2540,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B78" s="2" t="n">
         <v>43944</v>
@@ -2567,7 +2567,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B79" s="2" t="n">
         <v>43946</v>
@@ -2594,7 +2594,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B80" s="2" t="n">
         <v>43973</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B81" s="2" t="n">
         <v>43976</v>
@@ -2648,7 +2648,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B82" s="2" t="n">
         <v>43996</v>
@@ -2675,7 +2675,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B83" s="2" t="n">
         <v>44007</v>
@@ -2702,7 +2702,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B84" s="2" t="n">
         <v>44008</v>
@@ -2729,7 +2729,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B85" s="2" t="n">
         <v>44009</v>
@@ -2756,7 +2756,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B86" s="2" t="n">
         <v>44015</v>
@@ -2783,7 +2783,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B87" s="2" t="n">
         <v>44037</v>
@@ -2810,7 +2810,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B88" s="2" t="n">
         <v>44038</v>
@@ -2837,7 +2837,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B89" s="2" t="n">
         <v>44040</v>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B90" s="2" t="n">
         <v>44042</v>
@@ -2891,7 +2891,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B91" s="2" t="n">
         <v>44042</v>
@@ -2918,7 +2918,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B92" s="2" t="n">
         <v>44043</v>
@@ -2945,7 +2945,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B93" s="2" t="n">
         <v>44043</v>
@@ -2972,7 +2972,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B94" s="2" t="n">
         <v>44048</v>
@@ -2999,61 +2999,61 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B95" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sisa Konsumsi Panitia</t>
+          <t>Infaq ustadz Khotib Jum'at 6 Agustus 2020</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Konsumsi &amp; Kegiatan</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>141000</v>
+        <v>0</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>8391890</v>
+        <v>7641890</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B96" s="2" t="n">
         <v>44049</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Infaq ustadz Khotib Jum'at 6 Agustus 2020</t>
+          <t>Sisa Konsumsi Panitia</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Konsumsi &amp; Kegiatan</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>0</v>
+        <v>141000</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>7641890</v>
+        <v>8391890</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B97" s="2" t="n">
         <v>44068</v>
@@ -3080,7 +3080,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B98" s="2" t="n">
         <v>44071</v>
@@ -3107,7 +3107,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B99" s="2" t="n">
         <v>44085</v>
@@ -3134,7 +3134,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B100" s="2" t="n">
         <v>44099</v>
@@ -3161,7 +3161,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B101" s="2" t="n">
         <v>44099</v>
@@ -3188,7 +3188,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B102" s="2" t="n">
         <v>44113</v>
@@ -3215,61 +3215,61 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B103" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Khotib Jum'at</t>
+          <t>Pembukaan Kotak Amal Bergerak</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>2102000</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>5291890</v>
+        <v>7393890</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B104" s="2" t="n">
         <v>44120</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Amal Bergerak</t>
+          <t>Infaq Ustadz Khotib Jum'at</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>2102000</v>
+        <v>0</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>7393890</v>
+        <v>5291890</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B105" s="2" t="n">
         <v>44120</v>
@@ -3296,61 +3296,61 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B106" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Khotib Jum'at</t>
+          <t>Pembukaan Kencleng Masjid 23 Oktober 2020</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>10893890</v>
+        <v>11243890</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B107" s="2" t="n">
         <v>44127</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pembukaan Kencleng Masjid 23 Oktober 2020</t>
+          <t>Infaq Ustadz Khotib Jum'at</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>11243890</v>
+        <v>10893890</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B108" s="2" t="n">
         <v>44134</v>
@@ -3377,7 +3377,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B109" s="2" t="n">
         <v>44134</v>
@@ -3404,7 +3404,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B110" s="2" t="n">
         <v>44140</v>
@@ -3431,7 +3431,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B111" s="2" t="n">
         <v>44148</v>
@@ -3458,7 +3458,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B112" s="2" t="n">
         <v>44155</v>
@@ -3485,7 +3485,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B113" s="2" t="n">
         <v>44160</v>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="B114" s="2" t="n">
         <v>44160</v>
@@ -3538,7 +3538,9 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
       <c r="B115" s="2" t="n">
         <v>44162</v>
       </c>
@@ -3564,7 +3566,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="B116" s="2" t="n">
         <v>44165</v>
@@ -3590,7 +3592,9 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
       <c r="B117" s="2" t="n">
         <v>44183</v>
       </c>
@@ -3615,7 +3619,9 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
       <c r="B118" s="2" t="n">
         <v>44184</v>
       </c>
@@ -3640,7 +3646,9 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
       <c r="B119" s="2" t="n">
         <v>44185</v>
       </c>
@@ -3665,7 +3673,9 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
       <c r="B120" s="2" t="n">
         <v>44185</v>
       </c>
@@ -3690,7 +3700,9 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
       <c r="B121" s="2" t="n">
         <v>44190</v>
       </c>
@@ -3716,7 +3728,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="B122" s="2" t="n">
         <v>44198</v>
@@ -3743,7 +3755,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B123" s="2" t="n">
         <v>44198</v>
@@ -3770,7 +3782,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="B124" s="2" t="n">
         <v>44212</v>
@@ -3796,7 +3808,9 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
       <c r="B125" s="2" t="n">
         <v>44213</v>
       </c>
@@ -3822,7 +3836,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B126" s="2" t="n">
         <v>44221</v>
@@ -3848,7 +3862,9 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
       <c r="B127" s="2" t="n">
         <v>44225</v>
       </c>
@@ -3874,7 +3890,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>114</v>
+        <v>127</v>
       </c>
       <c r="B128" s="2" t="n">
         <v>44229</v>
@@ -3900,7 +3916,9 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
       <c r="B129" s="2" t="n">
         <v>44246</v>
       </c>
@@ -3925,7 +3943,9 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
       <c r="B130" s="2" t="n">
         <v>44247</v>
       </c>
@@ -3951,7 +3971,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>115</v>
+        <v>130</v>
       </c>
       <c r="B131" s="2" t="n">
         <v>44252</v>
@@ -3977,7 +3997,9 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
       <c r="B132" s="2" t="n">
         <v>44253</v>
       </c>
@@ -4003,7 +4025,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="B133" s="2" t="n">
         <v>44267</v>
@@ -4030,7 +4052,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B134" s="2" t="n">
         <v>44269</v>
@@ -4057,7 +4079,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="B135" s="2" t="n">
         <v>44274</v>
@@ -4084,7 +4106,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="B136" s="2" t="n">
         <v>44280</v>
@@ -4111,7 +4133,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B137" s="2" t="n">
         <v>44281</v>
@@ -4138,7 +4160,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="B138" s="2" t="n">
         <v>44288</v>
@@ -4165,7 +4187,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B139" s="2" t="n">
         <v>44295</v>
@@ -4192,7 +4214,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B140" s="2" t="n">
         <v>44296</v>
@@ -4219,7 +4241,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B141" s="2" t="n">
         <v>44298</v>
@@ -4246,7 +4268,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B142" s="2" t="n">
         <v>44300</v>
@@ -4273,7 +4295,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>126</v>
+        <v>142</v>
       </c>
       <c r="B143" s="2" t="n">
         <v>44302</v>
@@ -4300,7 +4322,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>127</v>
+        <v>143</v>
       </c>
       <c r="B144" s="2" t="n">
         <v>44303</v>
@@ -4327,7 +4349,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="B145" s="2" t="n">
         <v>44304</v>
@@ -4354,7 +4376,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="B146" s="2" t="n">
         <v>44307</v>
@@ -4381,7 +4403,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="B147" s="2" t="n">
         <v>44309</v>
@@ -4408,7 +4430,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="B148" s="2" t="n">
         <v>44310</v>
@@ -4435,61 +4457,61 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="B149" s="2" t="n">
         <v>44311</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni April + THR</t>
+          <t>Material dan Jasa Renovasi Atap</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Renovasi &amp; Aset Masjid</t>
         </is>
       </c>
       <c r="E149" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>900000</v>
+        <v>5971000</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>15659290</v>
+        <v>9688290</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="B150" s="2" t="n">
         <v>44311</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Material dan Jasa Renovasi Atap</t>
+          <t>Gaji Bang Zaeni April + THR</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Renovasi &amp; Aset Masjid</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E150" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>5971000</v>
+        <v>900000</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>9688290</v>
+        <v>15659290</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="B151" s="2" t="n">
         <v>44312</v>
@@ -4516,7 +4538,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B152" s="2" t="n">
         <v>44313</v>
@@ -4543,7 +4565,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="B153" s="2" t="n">
         <v>44316</v>
@@ -4570,7 +4592,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="B154" s="2" t="n">
         <v>44316</v>
@@ -4597,7 +4619,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="B155" s="2" t="n">
         <v>44317</v>
@@ -4623,7 +4645,9 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr"/>
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
       <c r="B156" s="2" t="n">
         <v>44319</v>
       </c>
@@ -4649,7 +4673,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B157" s="2" t="n">
         <v>44321</v>
@@ -4676,7 +4700,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="B158" s="2" t="n">
         <v>44322</v>
@@ -4703,34 +4727,34 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>141</v>
+        <v>160</v>
       </c>
       <c r="B159" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Beli Gorden Hijab</t>
+          <t>Ceramah Tarawih</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E159" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>9754290</v>
+        <v>8754290</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B160" s="2" t="n">
         <v>44323</v>
@@ -4757,34 +4781,34 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="B161" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ceramah Tarawih</t>
+          <t>Beli Gorden Hijab</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>8754290</v>
+        <v>9754290</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="B162" s="2" t="n">
         <v>44324</v>
@@ -4811,7 +4835,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="B163" s="2" t="n">
         <v>44327</v>
@@ -4838,7 +4862,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>146</v>
+        <v>163</v>
       </c>
       <c r="B164" s="2" t="n">
         <v>44328</v>
@@ -4865,7 +4889,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="B165" s="2" t="n">
         <v>44329</v>
@@ -4892,7 +4916,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="B166" s="2" t="n">
         <v>44329</v>
@@ -4919,7 +4943,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>149</v>
+        <v>166</v>
       </c>
       <c r="B167" s="2" t="n">
         <v>44330</v>
@@ -4946,7 +4970,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="B168" s="2" t="n">
         <v>44336</v>
@@ -4973,7 +4997,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>151</v>
+        <v>168</v>
       </c>
       <c r="B169" s="2" t="n">
         <v>44344</v>
@@ -5000,7 +5024,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B170" s="2" t="n">
         <v>44344</v>
@@ -5027,7 +5051,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>153</v>
+        <v>170</v>
       </c>
       <c r="B171" s="2" t="n">
         <v>44351</v>
@@ -5054,7 +5078,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>154</v>
+        <v>171</v>
       </c>
       <c r="B172" s="2" t="n">
         <v>44352</v>
@@ -5081,7 +5105,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>155</v>
+        <v>172</v>
       </c>
       <c r="B173" s="2" t="n">
         <v>44354</v>
@@ -5108,7 +5132,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>156</v>
+        <v>173</v>
       </c>
       <c r="B174" s="2" t="n">
         <v>44358</v>
@@ -5135,7 +5159,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>157</v>
+        <v>174</v>
       </c>
       <c r="B175" s="2" t="n">
         <v>44363</v>
@@ -5162,7 +5186,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="B176" s="2" t="n">
         <v>44365</v>
@@ -5189,7 +5213,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>159</v>
+        <v>176</v>
       </c>
       <c r="B177" s="2" t="n">
         <v>44372</v>
@@ -5216,7 +5240,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>160</v>
+        <v>177</v>
       </c>
       <c r="B178" s="2" t="n">
         <v>44372</v>
@@ -5243,7 +5267,7 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>161</v>
+        <v>178</v>
       </c>
       <c r="B179" s="2" t="n">
         <v>44372</v>
@@ -5270,7 +5294,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>162</v>
+        <v>179</v>
       </c>
       <c r="B180" s="2" t="n">
         <v>44402</v>
@@ -5297,7 +5321,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B181" s="2" t="n">
         <v>44414</v>
@@ -5324,7 +5348,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="B182" s="2" t="n">
         <v>44421</v>
@@ -5351,7 +5375,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="B183" s="2" t="n">
         <v>44422</v>
@@ -5378,7 +5402,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>156</v>
+        <v>183</v>
       </c>
       <c r="B184" s="2" t="n">
         <v>44428</v>
@@ -5405,7 +5429,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>157</v>
+        <v>184</v>
       </c>
       <c r="B185" s="2" t="n">
         <v>44433</v>
@@ -5432,7 +5456,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>158</v>
+        <v>185</v>
       </c>
       <c r="B186" s="2" t="n">
         <v>44435</v>
@@ -5459,7 +5483,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>159</v>
+        <v>186</v>
       </c>
       <c r="B187" s="2" t="n">
         <v>44442</v>
@@ -5486,7 +5510,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>160</v>
+        <v>187</v>
       </c>
       <c r="B188" s="2" t="n">
         <v>44449</v>
@@ -5513,7 +5537,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>161</v>
+        <v>188</v>
       </c>
       <c r="B189" s="2" t="n">
         <v>44456</v>
@@ -5540,7 +5564,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>162</v>
+        <v>189</v>
       </c>
       <c r="B190" s="2" t="n">
         <v>44463</v>
@@ -5567,7 +5591,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>163</v>
+        <v>190</v>
       </c>
       <c r="B191" s="2" t="n">
         <v>44464</v>
@@ -5594,7 +5618,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="B192" s="2" t="n">
         <v>44491</v>
@@ -5621,7 +5645,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="B193" s="2" t="n">
         <v>44494</v>
@@ -5648,7 +5672,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>166</v>
+        <v>193</v>
       </c>
       <c r="B194" s="2" t="n">
         <v>44507</v>
@@ -5675,7 +5699,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="B195" s="2" t="n">
         <v>44517</v>
@@ -5702,7 +5726,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="B196" s="2" t="n">
         <v>44525</v>
@@ -5729,7 +5753,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>169</v>
+        <v>196</v>
       </c>
       <c r="B197" s="2" t="n">
         <v>44539</v>
@@ -5756,7 +5780,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>170</v>
+        <v>197</v>
       </c>
       <c r="B198" s="2" t="n">
         <v>44555</v>
@@ -5783,7 +5807,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>171</v>
+        <v>198</v>
       </c>
       <c r="B199" s="2" t="n">
         <v>44571</v>
@@ -5810,7 +5834,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="B200" s="2" t="n">
         <v>44581</v>
@@ -5837,7 +5861,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="B201" s="2" t="n">
         <v>44585</v>
@@ -5864,7 +5888,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="B202" s="2" t="n">
         <v>44586</v>
@@ -5891,7 +5915,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>175</v>
+        <v>202</v>
       </c>
       <c r="B203" s="2" t="n">
         <v>44603</v>
@@ -5918,7 +5942,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>176</v>
+        <v>203</v>
       </c>
       <c r="B204" s="2" t="n">
         <v>44604</v>
@@ -5945,7 +5969,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>177</v>
+        <v>204</v>
       </c>
       <c r="B205" s="2" t="n">
         <v>44620</v>
@@ -5972,7 +5996,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>178</v>
+        <v>205</v>
       </c>
       <c r="B206" s="2" t="n">
         <v>44623</v>
@@ -5999,7 +6023,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>179</v>
+        <v>206</v>
       </c>
       <c r="B207" s="2" t="n">
         <v>44632</v>
@@ -6026,7 +6050,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>180</v>
+        <v>207</v>
       </c>
       <c r="B208" s="2" t="n">
         <v>44632</v>
@@ -6053,7 +6077,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>181</v>
+        <v>208</v>
       </c>
       <c r="B209" s="2" t="n">
         <v>44633</v>
@@ -6080,7 +6104,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>182</v>
+        <v>209</v>
       </c>
       <c r="B210" s="2" t="n">
         <v>44634</v>
@@ -6107,7 +6131,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>183</v>
+        <v>210</v>
       </c>
       <c r="B211" s="2" t="n">
         <v>44643</v>
@@ -6134,61 +6158,61 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>184</v>
+        <v>212</v>
       </c>
       <c r="B212" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Sholat Jum'at</t>
+          <t>Jasa Bersihin Karpet</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Renovasi &amp; Aset Masjid</t>
         </is>
       </c>
       <c r="E212" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>300000</v>
+        <v>825000</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>14400390</v>
+        <v>13575390</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="B213" s="2" t="n">
         <v>44645</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Jasa Bersihin Karpet</t>
+          <t>Infaq Ustadz Sholat Jum'at</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Renovasi &amp; Aset Masjid</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E213" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>825000</v>
+        <v>300000</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>13575390</v>
+        <v>14400390</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>186</v>
+        <v>213</v>
       </c>
       <c r="B214" s="2" t="n">
         <v>44646</v>
@@ -6215,7 +6239,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>187</v>
+        <v>214</v>
       </c>
       <c r="B215" s="2" t="n">
         <v>44646</v>
@@ -6242,7 +6266,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>188</v>
+        <v>215</v>
       </c>
       <c r="B216" s="2" t="n">
         <v>44647</v>
@@ -6269,7 +6293,7 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>189</v>
+        <v>216</v>
       </c>
       <c r="B217" s="2" t="n">
         <v>44652</v>
@@ -6296,7 +6320,7 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>190</v>
+        <v>217</v>
       </c>
       <c r="B218" s="2" t="n">
         <v>44652</v>
@@ -6323,7 +6347,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>191</v>
+        <v>218</v>
       </c>
       <c r="B219" s="2" t="n">
         <v>44653</v>
@@ -6350,7 +6374,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>192</v>
+        <v>219</v>
       </c>
       <c r="B220" s="2" t="n">
         <v>44654</v>
@@ -6377,7 +6401,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>193</v>
+        <v>220</v>
       </c>
       <c r="B221" s="2" t="n">
         <v>44657</v>
@@ -6404,7 +6428,7 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="B222" s="2" t="n">
         <v>44659</v>
@@ -6431,7 +6455,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>195</v>
+        <v>222</v>
       </c>
       <c r="B223" s="2" t="n">
         <v>44660</v>
@@ -6458,7 +6482,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>196</v>
+        <v>223</v>
       </c>
       <c r="B224" s="2" t="n">
         <v>44661</v>
@@ -6485,7 +6509,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="B225" s="2" t="n">
         <v>44666</v>
@@ -6512,7 +6536,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>198</v>
+        <v>225</v>
       </c>
       <c r="B226" s="2" t="n">
         <v>44667</v>
@@ -6539,7 +6563,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>199</v>
+        <v>226</v>
       </c>
       <c r="B227" s="2" t="n">
         <v>44668</v>
@@ -6566,7 +6590,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="B228" s="2" t="n">
         <v>44668</v>
@@ -6593,7 +6617,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>201</v>
+        <v>228</v>
       </c>
       <c r="B229" s="2" t="n">
         <v>44670</v>
@@ -6620,7 +6644,7 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="B230" s="2" t="n">
         <v>44673</v>
@@ -6647,7 +6671,7 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>203</v>
+        <v>230</v>
       </c>
       <c r="B231" s="2" t="n">
         <v>44673</v>
@@ -6674,7 +6698,7 @@
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>204</v>
+        <v>231</v>
       </c>
       <c r="B232" s="2" t="n">
         <v>44674</v>
@@ -6701,7 +6725,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>205</v>
+        <v>232</v>
       </c>
       <c r="B233" s="2" t="n">
         <v>44675</v>
@@ -6728,7 +6752,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>206</v>
+        <v>233</v>
       </c>
       <c r="B234" s="2" t="n">
         <v>44676</v>
@@ -6755,7 +6779,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>207</v>
+        <v>234</v>
       </c>
       <c r="B235" s="2" t="n">
         <v>44680</v>
@@ -6782,7 +6806,7 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>208</v>
+        <v>235</v>
       </c>
       <c r="B236" s="2" t="n">
         <v>44681</v>
@@ -6809,7 +6833,7 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>209</v>
+        <v>236</v>
       </c>
       <c r="B237" s="2" t="n">
         <v>44682</v>
@@ -6836,7 +6860,7 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>210</v>
+        <v>237</v>
       </c>
       <c r="B238" s="2" t="n">
         <v>44684</v>
@@ -6863,7 +6887,7 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>211</v>
+        <v>238</v>
       </c>
       <c r="B239" s="2" t="n">
         <v>44706</v>
@@ -6890,7 +6914,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>212</v>
+        <v>239</v>
       </c>
       <c r="B240" s="2" t="n">
         <v>44710</v>
@@ -6917,7 +6941,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>213</v>
+        <v>240</v>
       </c>
       <c r="B241" s="2" t="n">
         <v>44719</v>
@@ -6944,7 +6968,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>214</v>
+        <v>241</v>
       </c>
       <c r="B242" s="2" t="n">
         <v>44722</v>
@@ -6971,7 +6995,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>215</v>
+        <v>242</v>
       </c>
       <c r="B243" s="2" t="n">
         <v>44722</v>
@@ -6998,7 +7022,7 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>216</v>
+        <v>243</v>
       </c>
       <c r="B244" s="2" t="n">
         <v>44723</v>
@@ -7025,7 +7049,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>217</v>
+        <v>244</v>
       </c>
       <c r="B245" s="2" t="n">
         <v>44737</v>
@@ -7052,7 +7076,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="B246" s="2" t="n">
         <v>44743</v>
@@ -7079,7 +7103,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="B247" s="2" t="n">
         <v>44749</v>
@@ -7106,7 +7130,7 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>220</v>
+        <v>247</v>
       </c>
       <c r="B248" s="2" t="n">
         <v>44750</v>
@@ -7133,7 +7157,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="B249" s="2" t="n">
         <v>44751</v>
@@ -7160,7 +7184,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>222</v>
+        <v>249</v>
       </c>
       <c r="B250" s="2" t="n">
         <v>44752</v>
@@ -7187,7 +7211,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="B251" s="2" t="n">
         <v>44753</v>
@@ -7214,7 +7238,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>224</v>
+        <v>251</v>
       </c>
       <c r="B252" s="2" t="n">
         <v>44770</v>
@@ -7241,7 +7265,7 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>225</v>
+        <v>252</v>
       </c>
       <c r="B253" s="2" t="n">
         <v>44771</v>
@@ -7268,7 +7292,7 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>226</v>
+        <v>253</v>
       </c>
       <c r="B254" s="2" t="n">
         <v>44781</v>
@@ -7295,7 +7319,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>227</v>
+        <v>254</v>
       </c>
       <c r="B255" s="2" t="n">
         <v>44786</v>
@@ -7322,7 +7346,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>228</v>
+        <v>255</v>
       </c>
       <c r="B256" s="2" t="n">
         <v>44798</v>
@@ -7349,7 +7373,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>229</v>
+        <v>256</v>
       </c>
       <c r="B257" s="2" t="n">
         <v>44806</v>
@@ -7376,7 +7400,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="B258" s="2" t="n">
         <v>44810</v>
@@ -7403,7 +7427,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>231</v>
+        <v>258</v>
       </c>
       <c r="B259" s="2" t="n">
         <v>44828</v>
@@ -7430,7 +7454,7 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>232</v>
+        <v>259</v>
       </c>
       <c r="B260" s="2" t="n">
         <v>44829</v>
@@ -7457,7 +7481,7 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>233</v>
+        <v>260</v>
       </c>
       <c r="B261" s="2" t="n">
         <v>44836</v>
@@ -7484,7 +7508,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>234</v>
+        <v>261</v>
       </c>
       <c r="B262" s="2" t="n">
         <v>44837</v>
@@ -7511,7 +7535,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>235</v>
+        <v>262</v>
       </c>
       <c r="B263" s="2" t="n">
         <v>44842</v>
@@ -7538,7 +7562,7 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>236</v>
+        <v>263</v>
       </c>
       <c r="B264" s="2" t="n">
         <v>44843</v>
@@ -7565,7 +7589,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>237</v>
+        <v>264</v>
       </c>
       <c r="B265" s="2" t="n">
         <v>44843</v>
@@ -7592,7 +7616,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>238</v>
+        <v>265</v>
       </c>
       <c r="B266" s="2" t="n">
         <v>44855</v>
@@ -7619,7 +7643,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="B267" s="2" t="n">
         <v>44861</v>
@@ -7646,7 +7670,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>240</v>
+        <v>267</v>
       </c>
       <c r="B268" s="2" t="n">
         <v>44862</v>
@@ -7673,7 +7697,7 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>241</v>
+        <v>268</v>
       </c>
       <c r="B269" s="2" t="n">
         <v>44867</v>
@@ -7700,7 +7724,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>242</v>
+        <v>269</v>
       </c>
       <c r="B270" s="2" t="n">
         <v>44878</v>
@@ -7727,7 +7751,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>243</v>
+        <v>270</v>
       </c>
       <c r="B271" s="2" t="n">
         <v>44881</v>
@@ -7754,7 +7778,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>244</v>
+        <v>271</v>
       </c>
       <c r="B272" s="2" t="n">
         <v>44890</v>
@@ -7781,7 +7805,7 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>245</v>
+        <v>272</v>
       </c>
       <c r="B273" s="2" t="n">
         <v>44897</v>
@@ -7808,7 +7832,7 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>246</v>
+        <v>273</v>
       </c>
       <c r="B274" s="2" t="n">
         <v>44899</v>
@@ -7835,7 +7859,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>247</v>
+        <v>274</v>
       </c>
       <c r="B275" s="2" t="n">
         <v>44920</v>
@@ -7862,7 +7886,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>248</v>
+        <v>275</v>
       </c>
       <c r="B276" s="2" t="n">
         <v>44921</v>
@@ -7889,7 +7913,7 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>249</v>
+        <v>276</v>
       </c>
       <c r="B277" s="2" t="n">
         <v>44927</v>
@@ -7916,7 +7940,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>250</v>
+        <v>277</v>
       </c>
       <c r="B278" s="2" t="n">
         <v>44929</v>
@@ -7943,7 +7967,7 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>251</v>
+        <v>278</v>
       </c>
       <c r="B279" s="2" t="n">
         <v>44942</v>
@@ -7970,7 +7994,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>252</v>
+        <v>279</v>
       </c>
       <c r="B280" s="2" t="n">
         <v>44951</v>
@@ -7997,7 +8021,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>253</v>
+        <v>280</v>
       </c>
       <c r="B281" s="2" t="n">
         <v>44955</v>
@@ -8024,7 +8048,7 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>254</v>
+        <v>281</v>
       </c>
       <c r="B282" s="2" t="n">
         <v>44958</v>
@@ -8051,7 +8075,7 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>255</v>
+        <v>282</v>
       </c>
       <c r="B283" s="2" t="n">
         <v>44961</v>
@@ -8078,7 +8102,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>256</v>
+        <v>283</v>
       </c>
       <c r="B284" s="2" t="n">
         <v>44968</v>
@@ -8105,7 +8129,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>257</v>
+        <v>284</v>
       </c>
       <c r="B285" s="2" t="n">
         <v>44973</v>
@@ -8132,7 +8156,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>258</v>
+        <v>285</v>
       </c>
       <c r="B286" s="2" t="n">
         <v>44973</v>
@@ -8159,7 +8183,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>259</v>
+        <v>286</v>
       </c>
       <c r="B287" s="2" t="n">
         <v>44975</v>
@@ -8186,7 +8210,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>260</v>
+        <v>287</v>
       </c>
       <c r="B288" s="2" t="n">
         <v>44982</v>
@@ -8213,7 +8237,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>261</v>
+        <v>288</v>
       </c>
       <c r="B289" s="2" t="n">
         <v>44983</v>
@@ -8240,7 +8264,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>262</v>
+        <v>289</v>
       </c>
       <c r="B290" s="2" t="n">
         <v>44986</v>
@@ -8267,7 +8291,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>263</v>
+        <v>290</v>
       </c>
       <c r="B291" s="2" t="n">
         <v>44989</v>
@@ -8294,7 +8318,7 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="B292" s="2" t="n">
         <v>44990</v>
@@ -8321,7 +8345,7 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>265</v>
+        <v>292</v>
       </c>
       <c r="B293" s="2" t="n">
         <v>44990</v>
@@ -8348,7 +8372,7 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>266</v>
+        <v>293</v>
       </c>
       <c r="B294" s="2" t="n">
         <v>44992</v>
@@ -8375,7 +8399,7 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>267</v>
+        <v>294</v>
       </c>
       <c r="B295" s="2" t="n">
         <v>44994</v>
@@ -8402,7 +8426,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>268</v>
+        <v>295</v>
       </c>
       <c r="B296" s="2" t="n">
         <v>44994</v>
@@ -8429,7 +8453,7 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>269</v>
+        <v>296</v>
       </c>
       <c r="B297" s="2" t="n">
         <v>44994</v>
@@ -8456,7 +8480,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="B298" s="2" t="n">
         <v>44996</v>
@@ -8483,7 +8507,7 @@
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="B299" s="2" t="n">
         <v>44997</v>
@@ -8510,7 +8534,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>272</v>
+        <v>299</v>
       </c>
       <c r="B300" s="2" t="n">
         <v>44998</v>
@@ -8537,7 +8561,7 @@
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>273</v>
+        <v>300</v>
       </c>
       <c r="B301" s="2" t="n">
         <v>45004</v>
@@ -8564,7 +8588,7 @@
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>274</v>
+        <v>301</v>
       </c>
       <c r="B302" s="2" t="n">
         <v>45008</v>
@@ -8591,7 +8615,7 @@
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>275</v>
+        <v>302</v>
       </c>
       <c r="B303" s="2" t="n">
         <v>45009</v>
@@ -8618,7 +8642,7 @@
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>276</v>
+        <v>303</v>
       </c>
       <c r="B304" s="2" t="n">
         <v>45009</v>
@@ -8645,7 +8669,7 @@
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>277</v>
+        <v>304</v>
       </c>
       <c r="B305" s="2" t="n">
         <v>45010</v>
@@ -8672,7 +8696,7 @@
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>278</v>
+        <v>305</v>
       </c>
       <c r="B306" s="2" t="n">
         <v>45011</v>
@@ -8699,7 +8723,7 @@
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>279</v>
+        <v>306</v>
       </c>
       <c r="B307" s="2" t="n">
         <v>45012</v>
@@ -8726,7 +8750,7 @@
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>280</v>
+        <v>307</v>
       </c>
       <c r="B308" s="2" t="n">
         <v>45013</v>
@@ -8753,7 +8777,7 @@
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>281</v>
+        <v>308</v>
       </c>
       <c r="B309" s="2" t="n">
         <v>45015</v>
@@ -8780,7 +8804,7 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>282</v>
+        <v>309</v>
       </c>
       <c r="B310" s="2" t="n">
         <v>45016</v>
@@ -8807,7 +8831,7 @@
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>283</v>
+        <v>310</v>
       </c>
       <c r="B311" s="2" t="n">
         <v>45016</v>
@@ -8834,7 +8858,7 @@
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>284</v>
+        <v>311</v>
       </c>
       <c r="B312" s="2" t="n">
         <v>45016</v>
@@ -8861,7 +8885,7 @@
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>285</v>
+        <v>312</v>
       </c>
       <c r="B313" s="2" t="n">
         <v>45017</v>
@@ -8888,7 +8912,7 @@
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="B314" s="2" t="n">
         <v>45017</v>
@@ -8915,7 +8939,7 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>287</v>
+        <v>314</v>
       </c>
       <c r="B315" s="2" t="n">
         <v>45017</v>
@@ -8942,7 +8966,7 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>288</v>
+        <v>315</v>
       </c>
       <c r="B316" s="2" t="n">
         <v>45018</v>
@@ -8969,7 +8993,7 @@
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>289</v>
+        <v>316</v>
       </c>
       <c r="B317" s="2" t="n">
         <v>45019</v>
@@ -8996,7 +9020,7 @@
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>290</v>
+        <v>317</v>
       </c>
       <c r="B318" s="2" t="n">
         <v>45019</v>
@@ -9023,7 +9047,7 @@
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>291</v>
+        <v>318</v>
       </c>
       <c r="B319" s="2" t="n">
         <v>45020</v>
@@ -9050,7 +9074,7 @@
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>292</v>
+        <v>319</v>
       </c>
       <c r="B320" s="2" t="n">
         <v>45021</v>
@@ -9077,7 +9101,7 @@
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>293</v>
+        <v>320</v>
       </c>
       <c r="B321" s="2" t="n">
         <v>45022</v>
@@ -9104,7 +9128,7 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="B322" s="2" t="n">
         <v>45023</v>
@@ -9131,7 +9155,7 @@
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>295</v>
+        <v>322</v>
       </c>
       <c r="B323" s="2" t="n">
         <v>45023</v>
@@ -9158,7 +9182,7 @@
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>296</v>
+        <v>323</v>
       </c>
       <c r="B324" s="2" t="n">
         <v>45024</v>
@@ -9185,7 +9209,7 @@
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>297</v>
+        <v>324</v>
       </c>
       <c r="B325" s="2" t="n">
         <v>45025</v>
@@ -9212,7 +9236,7 @@
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>298</v>
+        <v>325</v>
       </c>
       <c r="B326" s="2" t="n">
         <v>45026</v>
@@ -9239,7 +9263,7 @@
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="B327" s="2" t="n">
         <v>45026</v>
@@ -9266,7 +9290,7 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>300</v>
+        <v>327</v>
       </c>
       <c r="B328" s="2" t="n">
         <v>45027</v>
@@ -9293,7 +9317,7 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>301</v>
+        <v>328</v>
       </c>
       <c r="B329" s="2" t="n">
         <v>45028</v>
@@ -9320,7 +9344,7 @@
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>302</v>
+        <v>329</v>
       </c>
       <c r="B330" s="2" t="n">
         <v>45029</v>
@@ -9347,19 +9371,19 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>303</v>
+        <v>331</v>
       </c>
       <c r="B331" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Infaq Sholat Tarawih</t>
+          <t>Infaq Sholat Jum'at</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E331" s="3" t="n">
@@ -9369,24 +9393,24 @@
         <v>300000</v>
       </c>
       <c r="G331" s="3" t="n">
-        <v>10938390</v>
+        <v>10638390</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>304</v>
+        <v>330</v>
       </c>
       <c r="B332" s="2" t="n">
         <v>45030</v>
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Infaq Sholat Jum'at</t>
+          <t>Infaq Sholat Tarawih</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E332" s="3" t="n">
@@ -9396,12 +9420,12 @@
         <v>300000</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>10638390</v>
+        <v>10938390</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>305</v>
+        <v>332</v>
       </c>
       <c r="B333" s="2" t="n">
         <v>45032</v>
@@ -9428,7 +9452,7 @@
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>306</v>
+        <v>333</v>
       </c>
       <c r="B334" s="2" t="n">
         <v>45032</v>
@@ -9455,7 +9479,7 @@
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>307</v>
+        <v>334</v>
       </c>
       <c r="B335" s="2" t="n">
         <v>45033</v>
@@ -9482,7 +9506,7 @@
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>308</v>
+        <v>335</v>
       </c>
       <c r="B336" s="2" t="n">
         <v>45034</v>
@@ -9509,7 +9533,7 @@
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="B337" s="2" t="n">
         <v>45036</v>
@@ -9536,7 +9560,7 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>310</v>
+        <v>337</v>
       </c>
       <c r="B338" s="2" t="n">
         <v>45036</v>
@@ -9563,7 +9587,7 @@
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>311</v>
+        <v>338</v>
       </c>
       <c r="B339" s="2" t="n">
         <v>45036</v>
@@ -9590,7 +9614,7 @@
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>312</v>
+        <v>339</v>
       </c>
       <c r="B340" s="2" t="n">
         <v>45037</v>
@@ -9617,41 +9641,41 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>313</v>
+        <v>341</v>
       </c>
       <c r="B341" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Infaq Khotib Jum'at</t>
+          <t>Gaji Bang Zaeni Bulan April 2023</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E341" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F341" s="3" t="n">
-        <v>300000</v>
+        <v>600000</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>12649390</v>
+        <v>12049390</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>314</v>
+        <v>342</v>
       </c>
       <c r="B342" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan April 2023</t>
+          <t>THR ke Babe Kus</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
@@ -9663,42 +9687,42 @@
         <v>0</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>600000</v>
+        <v>1000000</v>
       </c>
       <c r="G342" s="3" t="n">
-        <v>12049390</v>
+        <v>11049390</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>315</v>
+        <v>340</v>
       </c>
       <c r="B343" s="2" t="n">
         <v>45044</v>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>THR ke Babe Kus</t>
+          <t>Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E343" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F343" s="3" t="n">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="G343" s="3" t="n">
-        <v>11049390</v>
+        <v>12649390</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>316</v>
+        <v>343</v>
       </c>
       <c r="B344" s="2" t="n">
         <v>45047</v>
@@ -9725,7 +9749,7 @@
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>317</v>
+        <v>344</v>
       </c>
       <c r="B345" s="2" t="n">
         <v>45051</v>
@@ -9752,7 +9776,7 @@
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>318</v>
+        <v>345</v>
       </c>
       <c r="B346" s="2" t="n">
         <v>45051</v>
@@ -9779,7 +9803,7 @@
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>319</v>
+        <v>346</v>
       </c>
       <c r="B347" s="2" t="n">
         <v>45056</v>
@@ -9806,7 +9830,7 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>320</v>
+        <v>347</v>
       </c>
       <c r="B348" s="2" t="n">
         <v>45059</v>
@@ -9833,7 +9857,7 @@
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>321</v>
+        <v>348</v>
       </c>
       <c r="B349" s="2" t="n">
         <v>45061</v>
@@ -9860,88 +9884,88 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="B350" s="2" t="n">
         <v>45064</v>
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Jasa Bongkar pasang tenda untuk 3 orang</t>
+          <t>Pembukaan Kotak Amal 18 Mei 2023</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E350" s="3" t="n">
-        <v>0</v>
+        <v>4267000</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="G350" s="3" t="n">
-        <v>12716390</v>
+        <v>14816390</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>322</v>
+        <v>351</v>
       </c>
       <c r="B351" s="2" t="n">
         <v>45064</v>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Amal 18 Mei 2023</t>
+          <t>Infaq Pembicara Halal Bihalal</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E351" s="3" t="n">
-        <v>4267000</v>
+        <v>0</v>
       </c>
       <c r="F351" s="3" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>14816390</v>
+        <v>13316390</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>323</v>
+        <v>349</v>
       </c>
       <c r="B352" s="2" t="n">
         <v>45064</v>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Infaq Pembicara Halal Bihalal</t>
+          <t>Jasa Bongkar pasang tenda untuk 3 orang</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E352" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F352" s="3" t="n">
-        <v>1500000</v>
+        <v>600000</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>13316390</v>
+        <v>12716390</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="B353" s="2" t="n">
         <v>45065</v>
@@ -9968,7 +9992,7 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>326</v>
+        <v>353</v>
       </c>
       <c r="B354" s="2" t="n">
         <v>45072</v>
@@ -9995,7 +10019,7 @@
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>327</v>
+        <v>354</v>
       </c>
       <c r="B355" s="2" t="n">
         <v>45072</v>
@@ -10022,7 +10046,7 @@
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>328</v>
+        <v>355</v>
       </c>
       <c r="B356" s="2" t="n">
         <v>45073</v>
@@ -10049,7 +10073,7 @@
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>329</v>
+        <v>356</v>
       </c>
       <c r="B357" s="2" t="n">
         <v>45079</v>
@@ -10076,7 +10100,7 @@
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="B358" s="2" t="n">
         <v>45079</v>
@@ -10103,7 +10127,7 @@
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="B359" s="2" t="n">
         <v>45082</v>
@@ -10130,7 +10154,7 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="B360" s="2" t="n">
         <v>45086</v>
@@ -10157,7 +10181,7 @@
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="B361" s="2" t="n">
         <v>45093</v>
@@ -10184,61 +10208,61 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>334</v>
+        <v>362</v>
       </c>
       <c r="B362" s="2" t="n">
         <v>45102</v>
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Amal 25 Juni 2023</t>
+          <t>Gaji Bang Zaeni Bulan Juni</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E362" s="3" t="n">
-        <v>5572000</v>
+        <v>0</v>
       </c>
       <c r="F362" s="3" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="G362" s="3" t="n">
-        <v>14583890</v>
+        <v>13983890</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>335</v>
+        <v>361</v>
       </c>
       <c r="B363" s="2" t="n">
         <v>45102</v>
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan Juni</t>
+          <t>Pembukaan Kotak Amal 25 Juni 2023</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E363" s="3" t="n">
-        <v>0</v>
+        <v>5572000</v>
       </c>
       <c r="F363" s="3" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="G363" s="3" t="n">
-        <v>13983890</v>
+        <v>14583890</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>336</v>
+        <v>363</v>
       </c>
       <c r="B364" s="2" t="n">
         <v>45103</v>
@@ -10265,7 +10289,7 @@
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>337</v>
+        <v>364</v>
       </c>
       <c r="B365" s="2" t="n">
         <v>45103</v>
@@ -10292,7 +10316,7 @@
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>338</v>
+        <v>365</v>
       </c>
       <c r="B366" s="2" t="n">
         <v>45107</v>
@@ -10319,7 +10343,7 @@
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>339</v>
+        <v>366</v>
       </c>
       <c r="B367" s="2" t="n">
         <v>45108</v>
@@ -10346,7 +10370,7 @@
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>340</v>
+        <v>367</v>
       </c>
       <c r="B368" s="2" t="n">
         <v>45109</v>
@@ -10373,7 +10397,7 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>341</v>
+        <v>368</v>
       </c>
       <c r="B369" s="2" t="n">
         <v>45109</v>
@@ -10400,7 +10424,7 @@
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>342</v>
+        <v>369</v>
       </c>
       <c r="B370" s="2" t="n">
         <v>45114</v>
@@ -10427,7 +10451,7 @@
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>343</v>
+        <v>370</v>
       </c>
       <c r="B371" s="2" t="n">
         <v>45121</v>
@@ -10454,7 +10478,7 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="B372" s="2" t="n">
         <v>45128</v>
@@ -10481,7 +10505,7 @@
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>345</v>
+        <v>372</v>
       </c>
       <c r="B373" s="2" t="n">
         <v>45132</v>
@@ -10508,7 +10532,7 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>346</v>
+        <v>373</v>
       </c>
       <c r="B374" s="2" t="n">
         <v>45135</v>
@@ -10535,7 +10559,7 @@
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>347</v>
+        <v>374</v>
       </c>
       <c r="B375" s="2" t="n">
         <v>45138</v>
@@ -10562,7 +10586,7 @@
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="B376" s="2" t="n">
         <v>45140</v>
@@ -10589,7 +10613,7 @@
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>349</v>
+        <v>376</v>
       </c>
       <c r="B377" s="2" t="n">
         <v>45142</v>
@@ -10616,7 +10640,7 @@
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>350</v>
+        <v>377</v>
       </c>
       <c r="B378" s="2" t="n">
         <v>45149</v>
@@ -10643,7 +10667,7 @@
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>351</v>
+        <v>378</v>
       </c>
       <c r="B379" s="2" t="n">
         <v>45151</v>
@@ -10670,7 +10694,7 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>352</v>
+        <v>379</v>
       </c>
       <c r="B380" s="2" t="n">
         <v>45156</v>
@@ -10697,7 +10721,7 @@
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>353</v>
+        <v>380</v>
       </c>
       <c r="B381" s="2" t="n">
         <v>45161</v>
@@ -10724,7 +10748,7 @@
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>354</v>
+        <v>381</v>
       </c>
       <c r="B382" s="2" t="n">
         <v>45163</v>
@@ -10751,7 +10775,7 @@
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>355</v>
+        <v>382</v>
       </c>
       <c r="B383" s="2" t="n">
         <v>45164</v>
@@ -10778,7 +10802,7 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>356</v>
+        <v>383</v>
       </c>
       <c r="B384" s="2" t="n">
         <v>45168</v>
@@ -10805,7 +10829,7 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>357</v>
+        <v>384</v>
       </c>
       <c r="B385" s="2" t="n">
         <v>45169</v>
@@ -10832,7 +10856,7 @@
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>358</v>
+        <v>385</v>
       </c>
       <c r="B386" s="2" t="n">
         <v>45170</v>
@@ -10859,7 +10883,7 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>359</v>
+        <v>386</v>
       </c>
       <c r="B387" s="2" t="n">
         <v>45171</v>
@@ -10886,7 +10910,7 @@
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>360</v>
+        <v>387</v>
       </c>
       <c r="B388" s="2" t="n">
         <v>45177</v>
@@ -10913,7 +10937,7 @@
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>361</v>
+        <v>388</v>
       </c>
       <c r="B389" s="2" t="n">
         <v>45184</v>
@@ -10940,7 +10964,7 @@
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>362</v>
+        <v>389</v>
       </c>
       <c r="B390" s="2" t="n">
         <v>45191</v>
@@ -10967,7 +10991,7 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>363</v>
+        <v>390</v>
       </c>
       <c r="B391" s="2" t="n">
         <v>45192</v>
@@ -10994,7 +11018,7 @@
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>364</v>
+        <v>391</v>
       </c>
       <c r="B392" s="2" t="n">
         <v>45195</v>
@@ -11021,7 +11045,7 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>365</v>
+        <v>392</v>
       </c>
       <c r="B393" s="2" t="n">
         <v>45198</v>
@@ -11048,7 +11072,7 @@
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>366</v>
+        <v>393</v>
       </c>
       <c r="B394" s="2" t="n">
         <v>45199</v>
@@ -11075,7 +11099,7 @@
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>367</v>
+        <v>394</v>
       </c>
       <c r="B395" s="2" t="n">
         <v>45200</v>
@@ -11102,7 +11126,7 @@
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>368</v>
+        <v>395</v>
       </c>
       <c r="B396" s="2" t="n">
         <v>45201</v>
@@ -11129,7 +11153,7 @@
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>369</v>
+        <v>396</v>
       </c>
       <c r="B397" s="2" t="n">
         <v>45205</v>
@@ -11156,7 +11180,7 @@
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>370</v>
+        <v>397</v>
       </c>
       <c r="B398" s="2" t="n">
         <v>45212</v>
@@ -11183,7 +11207,7 @@
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>371</v>
+        <v>398</v>
       </c>
       <c r="B399" s="2" t="n">
         <v>45219</v>
@@ -11210,7 +11234,7 @@
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>372</v>
+        <v>399</v>
       </c>
       <c r="B400" s="2" t="n">
         <v>45220</v>
@@ -11237,7 +11261,7 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="B401" s="2" t="n">
         <v>45226</v>
@@ -11264,7 +11288,7 @@
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="B402" s="2" t="n">
         <v>45227</v>
@@ -11291,7 +11315,7 @@
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>375</v>
+        <v>402</v>
       </c>
       <c r="B403" s="2" t="n">
         <v>45231</v>
@@ -11318,7 +11342,7 @@
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>376</v>
+        <v>403</v>
       </c>
       <c r="B404" s="2" t="n">
         <v>45232</v>
@@ -11345,7 +11369,7 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>377</v>
+        <v>404</v>
       </c>
       <c r="B405" s="2" t="n">
         <v>45233</v>
@@ -11372,7 +11396,7 @@
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>378</v>
+        <v>405</v>
       </c>
       <c r="B406" s="2" t="n">
         <v>45240</v>
@@ -11399,7 +11423,7 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>379</v>
+        <v>406</v>
       </c>
       <c r="B407" s="2" t="n">
         <v>45247</v>
@@ -11426,7 +11450,7 @@
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>380</v>
+        <v>407</v>
       </c>
       <c r="B408" s="2" t="n">
         <v>45254</v>
@@ -11453,7 +11477,7 @@
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>381</v>
+        <v>408</v>
       </c>
       <c r="B409" s="2" t="n">
         <v>45255</v>
@@ -11480,7 +11504,7 @@
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>382</v>
+        <v>409</v>
       </c>
       <c r="B410" s="2" t="n">
         <v>45261</v>
@@ -11507,7 +11531,7 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>383</v>
+        <v>410</v>
       </c>
       <c r="B411" s="2" t="n">
         <v>45261</v>
@@ -11534,7 +11558,7 @@
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>384</v>
+        <v>411</v>
       </c>
       <c r="B412" s="2" t="n">
         <v>45262</v>
@@ -11561,7 +11585,7 @@
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>385</v>
+        <v>412</v>
       </c>
       <c r="B413" s="2" t="n">
         <v>45268</v>
@@ -11588,7 +11612,7 @@
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>386</v>
+        <v>413</v>
       </c>
       <c r="B414" s="2" t="n">
         <v>45268</v>
@@ -11615,7 +11639,7 @@
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>387</v>
+        <v>414</v>
       </c>
       <c r="B415" s="2" t="n">
         <v>45268</v>
@@ -11642,7 +11666,7 @@
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>388</v>
+        <v>415</v>
       </c>
       <c r="B416" s="2" t="n">
         <v>45275</v>
@@ -11669,7 +11693,7 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>389</v>
+        <v>416</v>
       </c>
       <c r="B417" s="2" t="n">
         <v>45282</v>
@@ -11696,7 +11720,7 @@
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>390</v>
+        <v>417</v>
       </c>
       <c r="B418" s="2" t="n">
         <v>45283</v>
@@ -11723,7 +11747,7 @@
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>391</v>
+        <v>418</v>
       </c>
       <c r="B419" s="2" t="n">
         <v>45289</v>
@@ -11750,7 +11774,7 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>392</v>
+        <v>419</v>
       </c>
       <c r="B420" s="2" t="n">
         <v>45291</v>
@@ -11777,7 +11801,7 @@
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>393</v>
+        <v>420</v>
       </c>
       <c r="B421" s="2" t="n">
         <v>45291</v>
@@ -11804,7 +11828,7 @@
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>394</v>
+        <v>421</v>
       </c>
       <c r="B422" s="2" t="n">
         <v>45292</v>
@@ -11831,7 +11855,7 @@
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>395</v>
+        <v>422</v>
       </c>
       <c r="B423" s="2" t="n">
         <v>45296</v>
@@ -11858,7 +11882,7 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>396</v>
+        <v>423</v>
       </c>
       <c r="B424" s="2" t="n">
         <v>45303</v>
@@ -11885,7 +11909,7 @@
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>397</v>
+        <v>424</v>
       </c>
       <c r="B425" s="2" t="n">
         <v>45310</v>
@@ -11912,7 +11936,7 @@
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>398</v>
+        <v>425</v>
       </c>
       <c r="B426" s="2" t="n">
         <v>45317</v>
@@ -11939,7 +11963,7 @@
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>399</v>
+        <v>426</v>
       </c>
       <c r="B427" s="2" t="n">
         <v>45318</v>
@@ -11966,7 +11990,7 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>400</v>
+        <v>427</v>
       </c>
       <c r="B428" s="2" t="n">
         <v>45321</v>
@@ -11993,7 +12017,7 @@
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>401</v>
+        <v>428</v>
       </c>
       <c r="B429" s="2" t="n">
         <v>45322</v>
@@ -12020,7 +12044,7 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>402</v>
+        <v>429</v>
       </c>
       <c r="B430" s="2" t="n">
         <v>45324</v>
@@ -12047,7 +12071,7 @@
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>403</v>
+        <v>430</v>
       </c>
       <c r="B431" s="2" t="n">
         <v>45331</v>
@@ -12074,7 +12098,7 @@
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>404</v>
+        <v>431</v>
       </c>
       <c r="B432" s="2" t="n">
         <v>45332</v>
@@ -12101,7 +12125,7 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>405</v>
+        <v>432</v>
       </c>
       <c r="B433" s="2" t="n">
         <v>45338</v>
@@ -12128,7 +12152,7 @@
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>406</v>
+        <v>433</v>
       </c>
       <c r="B434" s="2" t="n">
         <v>45346</v>
@@ -12155,7 +12179,7 @@
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>407</v>
+        <v>434</v>
       </c>
       <c r="B435" s="2" t="n">
         <v>45347</v>
@@ -12182,7 +12206,7 @@
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="B436" s="2" t="n">
         <v>45349</v>
@@ -12209,7 +12233,7 @@
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>409</v>
+        <v>436</v>
       </c>
       <c r="B437" s="2" t="n">
         <v>45350</v>
@@ -12236,7 +12260,7 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>410</v>
+        <v>437</v>
       </c>
       <c r="B438" s="2" t="n">
         <v>45353</v>
@@ -12263,7 +12287,7 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>411</v>
+        <v>438</v>
       </c>
       <c r="B439" s="2" t="n">
         <v>45353</v>
@@ -12290,7 +12314,7 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>412</v>
+        <v>439</v>
       </c>
       <c r="B440" s="2" t="n">
         <v>45354</v>
@@ -12317,7 +12341,7 @@
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="B441" s="2" t="n">
         <v>45354</v>
@@ -12344,7 +12368,7 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>414</v>
+        <v>441</v>
       </c>
       <c r="B442" s="2" t="n">
         <v>45355</v>
@@ -12371,7 +12395,7 @@
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>415</v>
+        <v>442</v>
       </c>
       <c r="B443" s="2" t="n">
         <v>45358</v>
@@ -12398,7 +12422,7 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>416</v>
+        <v>443</v>
       </c>
       <c r="B444" s="2" t="n">
         <v>45362</v>
@@ -12425,7 +12449,7 @@
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>417</v>
+        <v>444</v>
       </c>
       <c r="B445" s="2" t="n">
         <v>45367</v>
@@ -12452,7 +12476,7 @@
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>418</v>
+        <v>445</v>
       </c>
       <c r="B446" s="2" t="n">
         <v>45367</v>
@@ -12479,7 +12503,7 @@
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>419</v>
+        <v>446</v>
       </c>
       <c r="B447" s="2" t="n">
         <v>45368</v>
@@ -12506,7 +12530,7 @@
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>420</v>
+        <v>447</v>
       </c>
       <c r="B448" s="2" t="n">
         <v>45374</v>
@@ -12533,7 +12557,7 @@
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>421</v>
+        <v>448</v>
       </c>
       <c r="B449" s="2" t="n">
         <v>45375</v>
@@ -12560,7 +12584,7 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="B450" s="2" t="n">
         <v>45379</v>
@@ -12587,7 +12611,7 @@
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>423</v>
+        <v>450</v>
       </c>
       <c r="B451" s="2" t="n">
         <v>45380</v>
@@ -12614,7 +12638,7 @@
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>424</v>
+        <v>451</v>
       </c>
       <c r="B452" s="2" t="n">
         <v>45381</v>
@@ -12641,7 +12665,7 @@
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>425</v>
+        <v>452</v>
       </c>
       <c r="B453" s="2" t="n">
         <v>45387</v>
@@ -12668,7 +12692,7 @@
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>426</v>
+        <v>453</v>
       </c>
       <c r="B454" s="2" t="n">
         <v>45401</v>
@@ -12695,7 +12719,7 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>427</v>
+        <v>454</v>
       </c>
       <c r="B455" s="2" t="n">
         <v>45402</v>
@@ -12722,7 +12746,7 @@
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="B456" s="2" t="n">
         <v>45407</v>
@@ -12749,7 +12773,7 @@
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>429</v>
+        <v>456</v>
       </c>
       <c r="B457" s="2" t="n">
         <v>45411</v>
@@ -12776,7 +12800,7 @@
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>430</v>
+        <v>457</v>
       </c>
       <c r="B458" s="2" t="n">
         <v>45412</v>
@@ -12803,7 +12827,7 @@
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>431</v>
+        <v>458</v>
       </c>
       <c r="B459" s="2" t="n">
         <v>45417</v>
@@ -12830,7 +12854,7 @@
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>433</v>
+        <v>459</v>
       </c>
       <c r="B460" s="2" t="n">
         <v>45440</v>
@@ -12857,7 +12881,7 @@
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>432</v>
+        <v>460</v>
       </c>
       <c r="B461" s="2" t="n">
         <v>45441</v>
@@ -12884,7 +12908,7 @@
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>434</v>
+        <v>461</v>
       </c>
       <c r="B462" s="2" t="n">
         <v>45442</v>
@@ -12911,7 +12935,7 @@
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>435</v>
+        <v>462</v>
       </c>
       <c r="B463" s="2" t="n">
         <v>45445</v>
@@ -12938,7 +12962,7 @@
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>436</v>
+        <v>463</v>
       </c>
       <c r="B464" s="2" t="n">
         <v>45459</v>
@@ -12965,7 +12989,7 @@
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>437</v>
+        <v>464</v>
       </c>
       <c r="B465" s="2" t="n">
         <v>45460</v>
@@ -12992,7 +13016,7 @@
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>438</v>
+        <v>465</v>
       </c>
       <c r="B466" s="2" t="n">
         <v>45468</v>
@@ -13019,7 +13043,7 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="B467" s="2" t="n">
         <v>45471</v>
@@ -13046,7 +13070,7 @@
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>440</v>
+        <v>467</v>
       </c>
       <c r="B468" s="2" t="n">
         <v>45474</v>
@@ -13073,7 +13097,7 @@
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>441</v>
+        <v>468</v>
       </c>
       <c r="B469" s="2" t="n">
         <v>45478</v>
@@ -13100,7 +13124,7 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>442</v>
+        <v>469</v>
       </c>
       <c r="B470" s="2" t="n">
         <v>45493</v>
@@ -13127,7 +13151,7 @@
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>443</v>
+        <v>470</v>
       </c>
       <c r="B471" s="2" t="n">
         <v>45497</v>
@@ -13154,7 +13178,7 @@
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>444</v>
+        <v>471</v>
       </c>
       <c r="B472" s="2" t="n">
         <v>45498</v>
@@ -13181,7 +13205,7 @@
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>445</v>
+        <v>472</v>
       </c>
       <c r="B473" s="2" t="n">
         <v>45500</v>
@@ -13208,7 +13232,7 @@
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>446</v>
+        <v>473</v>
       </c>
       <c r="B474" s="2" t="n">
         <v>45515</v>
@@ -13235,7 +13259,7 @@
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>447</v>
+        <v>474</v>
       </c>
       <c r="B475" s="2" t="n">
         <v>45529</v>
@@ -13262,7 +13286,7 @@
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>448</v>
+        <v>475</v>
       </c>
       <c r="B476" s="2" t="n">
         <v>45531</v>
@@ -13289,7 +13313,7 @@
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>449</v>
+        <v>476</v>
       </c>
       <c r="B477" s="2" t="n">
         <v>45534</v>
@@ -13316,7 +13340,7 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>450</v>
+        <v>477</v>
       </c>
       <c r="B478" s="2" t="n">
         <v>45535</v>
@@ -13343,7 +13367,7 @@
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="B479" s="2" t="n">
         <v>45540</v>
@@ -13370,7 +13394,7 @@
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="B480" s="2" t="n">
         <v>45547</v>
@@ -13397,7 +13421,7 @@
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="B481" s="2" t="n">
         <v>45550</v>
@@ -13424,7 +13448,7 @@
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>454</v>
+        <v>481</v>
       </c>
       <c r="B482" s="2" t="n">
         <v>45552</v>
@@ -13451,7 +13475,7 @@
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>455</v>
+        <v>482</v>
       </c>
       <c r="B483" s="2" t="n">
         <v>45556</v>
@@ -13478,7 +13502,7 @@
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>456</v>
+        <v>483</v>
       </c>
       <c r="B484" s="2" t="n">
         <v>45556</v>
@@ -13505,7 +13529,7 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>457</v>
+        <v>484</v>
       </c>
       <c r="B485" s="2" t="n">
         <v>45558</v>
@@ -13532,7 +13556,7 @@
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>458</v>
+        <v>485</v>
       </c>
       <c r="B486" s="2" t="n">
         <v>45558</v>
@@ -13559,7 +13583,7 @@
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>459</v>
+        <v>486</v>
       </c>
       <c r="B487" s="2" t="n">
         <v>45560</v>
@@ -13586,7 +13610,7 @@
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>460</v>
+        <v>487</v>
       </c>
       <c r="B488" s="2" t="n">
         <v>45563</v>
@@ -13613,7 +13637,7 @@
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="B489" s="2" t="n">
         <v>45565</v>
@@ -13640,7 +13664,7 @@
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>462</v>
+        <v>489</v>
       </c>
       <c r="B490" s="2" t="n">
         <v>45569</v>
@@ -13667,7 +13691,7 @@
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="B491" s="2" t="n">
         <v>45570</v>
@@ -13694,7 +13718,7 @@
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>464</v>
+        <v>491</v>
       </c>
       <c r="B492" s="2" t="n">
         <v>45581</v>
@@ -13721,7 +13745,7 @@
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="B493" s="2" t="n">
         <v>45584</v>
@@ -13748,7 +13772,7 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="B494" s="2" t="n">
         <v>45591</v>
@@ -13775,7 +13799,7 @@
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="B495" s="2" t="n">
         <v>45591</v>
@@ -13802,7 +13826,7 @@
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>468</v>
+        <v>495</v>
       </c>
       <c r="B496" s="2" t="n">
         <v>45595</v>
@@ -13829,7 +13853,7 @@
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>469</v>
+        <v>496</v>
       </c>
       <c r="B497" s="2" t="n">
         <v>45596</v>
@@ -13856,7 +13880,7 @@
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>470</v>
+        <v>497</v>
       </c>
       <c r="B498" s="2" t="n">
         <v>45601</v>
@@ -13883,7 +13907,7 @@
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>471</v>
+        <v>498</v>
       </c>
       <c r="B499" s="2" t="n">
         <v>45606</v>
@@ -13910,7 +13934,7 @@
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>472</v>
+        <v>499</v>
       </c>
       <c r="B500" s="2" t="n">
         <v>45610</v>
@@ -13937,7 +13961,7 @@
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>473</v>
+        <v>500</v>
       </c>
       <c r="B501" s="2" t="n">
         <v>45611</v>
@@ -13964,7 +13988,7 @@
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>474</v>
+        <v>501</v>
       </c>
       <c r="B502" s="2" t="n">
         <v>45622</v>
@@ -13991,7 +14015,7 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>475</v>
+        <v>502</v>
       </c>
       <c r="B503" s="2" t="n">
         <v>45623</v>
@@ -14018,7 +14042,7 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>476</v>
+        <v>503</v>
       </c>
       <c r="B504" s="2" t="n">
         <v>45624</v>
@@ -14045,7 +14069,7 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>477</v>
+        <v>504</v>
       </c>
       <c r="B505" s="2" t="n">
         <v>45626</v>
@@ -14072,7 +14096,7 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>478</v>
+        <v>505</v>
       </c>
       <c r="B506" s="2" t="n">
         <v>45651</v>
@@ -14099,7 +14123,7 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>479</v>
+        <v>506</v>
       </c>
       <c r="B507" s="2" t="n">
         <v>45654</v>
@@ -14126,7 +14150,7 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>480</v>
+        <v>507</v>
       </c>
       <c r="B508" s="2" t="n">
         <v>45656</v>
@@ -14153,7 +14177,7 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>481</v>
+        <v>508</v>
       </c>
       <c r="B509" s="2" t="n">
         <v>45660</v>
@@ -14180,7 +14204,7 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>482</v>
+        <v>509</v>
       </c>
       <c r="B510" s="2" t="n">
         <v>45675</v>
@@ -14207,7 +14231,7 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>483</v>
+        <v>510</v>
       </c>
       <c r="B511" s="2" t="n">
         <v>45676</v>
@@ -14234,7 +14258,7 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>484</v>
+        <v>511</v>
       </c>
       <c r="B512" s="2" t="n">
         <v>45682</v>
@@ -14261,7 +14285,7 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>485</v>
+        <v>512</v>
       </c>
       <c r="B513" s="2" t="n">
         <v>45684</v>
@@ -14288,7 +14312,7 @@
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>486</v>
+        <v>513</v>
       </c>
       <c r="B514" s="2" t="n">
         <v>45686</v>
@@ -14315,7 +14339,7 @@
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>487</v>
+        <v>514</v>
       </c>
       <c r="B515" s="2" t="n">
         <v>45687</v>
@@ -14342,7 +14366,7 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>488</v>
+        <v>515</v>
       </c>
       <c r="B516" s="2" t="n">
         <v>45696</v>
@@ -14369,7 +14393,7 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>489</v>
+        <v>516</v>
       </c>
       <c r="B517" s="2" t="n">
         <v>45696</v>
@@ -14396,7 +14420,7 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>490</v>
+        <v>517</v>
       </c>
       <c r="B518" s="2" t="n">
         <v>45697</v>
@@ -14423,7 +14447,7 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>491</v>
+        <v>518</v>
       </c>
       <c r="B519" s="2" t="n">
         <v>45702</v>
@@ -14450,7 +14474,7 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="B520" s="2" t="n">
         <v>45716</v>
@@ -14477,7 +14501,7 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>494</v>
+        <v>520</v>
       </c>
       <c r="B521" s="2" t="n">
         <v>45716</v>
@@ -14504,7 +14528,7 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>492</v>
+        <v>521</v>
       </c>
       <c r="B522" s="2" t="n">
         <v>45716</v>
@@ -14531,7 +14555,7 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>495</v>
+        <v>522</v>
       </c>
       <c r="B523" s="2" t="n">
         <v>45717</v>
@@ -14558,7 +14582,7 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>496</v>
+        <v>523</v>
       </c>
       <c r="B524" s="2" t="n">
         <v>45718</v>
@@ -14585,7 +14609,7 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="B525" s="2" t="n">
         <v>45719</v>
@@ -14612,7 +14636,7 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>498</v>
+        <v>525</v>
       </c>
       <c r="B526" s="2" t="n">
         <v>45721</v>
@@ -14639,7 +14663,7 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>499</v>
+        <v>526</v>
       </c>
       <c r="B527" s="2" t="n">
         <v>45724</v>
@@ -14666,7 +14690,7 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>500</v>
+        <v>527</v>
       </c>
       <c r="B528" s="2" t="n">
         <v>45724</v>
@@ -14693,7 +14717,7 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>501</v>
+        <v>528</v>
       </c>
       <c r="B529" s="2" t="n">
         <v>45725</v>
@@ -14720,7 +14744,7 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>502</v>
+        <v>529</v>
       </c>
       <c r="B530" s="2" t="n">
         <v>45728</v>
@@ -14747,7 +14771,7 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>503</v>
+        <v>530</v>
       </c>
       <c r="B531" s="2" t="n">
         <v>45730</v>
@@ -14774,7 +14798,7 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>505</v>
+        <v>531</v>
       </c>
       <c r="B532" s="2" t="n">
         <v>45731</v>
@@ -14801,7 +14825,7 @@
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>504</v>
+        <v>532</v>
       </c>
       <c r="B533" s="2" t="n">
         <v>45731</v>
@@ -14828,7 +14852,7 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>506</v>
+        <v>533</v>
       </c>
       <c r="B534" s="2" t="n">
         <v>45736</v>
@@ -14855,7 +14879,7 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>507</v>
+        <v>534</v>
       </c>
       <c r="B535" s="2" t="n">
         <v>45737</v>
@@ -14882,7 +14906,7 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>508</v>
+        <v>535</v>
       </c>
       <c r="B536" s="2" t="n">
         <v>45738</v>
@@ -14909,7 +14933,7 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>509</v>
+        <v>536</v>
       </c>
       <c r="B537" s="2" t="n">
         <v>45742</v>
@@ -14936,7 +14960,7 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>510</v>
+        <v>537</v>
       </c>
       <c r="B538" s="2" t="n">
         <v>45742</v>
@@ -14963,7 +14987,7 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>511</v>
+        <v>538</v>
       </c>
       <c r="B539" s="2" t="n">
         <v>45743</v>
@@ -14990,7 +15014,7 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>512</v>
+        <v>539</v>
       </c>
       <c r="B540" s="2" t="n">
         <v>45749</v>
@@ -15017,7 +15041,7 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>513</v>
+        <v>540</v>
       </c>
       <c r="B541" s="2" t="n">
         <v>45751</v>
@@ -15044,7 +15068,7 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>514</v>
+        <v>541</v>
       </c>
       <c r="B542" s="2" t="n">
         <v>45765</v>
@@ -15071,7 +15095,7 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>515</v>
+        <v>542</v>
       </c>
       <c r="B543" s="2" t="n">
         <v>45766</v>
@@ -15098,7 +15122,7 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>516</v>
+        <v>543</v>
       </c>
       <c r="B544" s="2" t="n">
         <v>45772</v>
@@ -15125,7 +15149,7 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="B545" s="2" t="n">
         <v>45773</v>
@@ -15152,7 +15176,7 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>518</v>
+        <v>545</v>
       </c>
       <c r="B546" s="2" t="n">
         <v>45773</v>
@@ -15179,7 +15203,7 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>519</v>
+        <v>546</v>
       </c>
       <c r="B547" s="2" t="n">
         <v>45774</v>
@@ -15206,7 +15230,7 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>520</v>
+        <v>547</v>
       </c>
       <c r="B548" s="2" t="n">
         <v>45777</v>
@@ -15233,7 +15257,7 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>521</v>
+        <v>548</v>
       </c>
       <c r="B549" s="2" t="n">
         <v>45779</v>
@@ -15260,7 +15284,7 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>522</v>
+        <v>549</v>
       </c>
       <c r="B550" s="2" t="n">
         <v>45780</v>
@@ -15287,7 +15311,7 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>524</v>
+        <v>550</v>
       </c>
       <c r="B551" s="2" t="n">
         <v>45790</v>
@@ -15314,7 +15338,7 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>523</v>
+        <v>551</v>
       </c>
       <c r="B552" s="2" t="n">
         <v>45790</v>
@@ -15341,7 +15365,7 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>525</v>
+        <v>552</v>
       </c>
       <c r="B553" s="2" t="n">
         <v>45791</v>
@@ -15368,7 +15392,7 @@
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>526</v>
+        <v>553</v>
       </c>
       <c r="B554" s="2" t="n">
         <v>45792</v>
@@ -15395,7 +15419,7 @@
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>527</v>
+        <v>554</v>
       </c>
       <c r="B555" s="2" t="n">
         <v>45800</v>
@@ -15422,7 +15446,7 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>528</v>
+        <v>555</v>
       </c>
       <c r="B556" s="2" t="n">
         <v>45802</v>
@@ -15449,7 +15473,7 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>529</v>
+        <v>556</v>
       </c>
       <c r="B557" s="2" t="n">
         <v>45802</v>
@@ -15476,7 +15500,7 @@
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>530</v>
+        <v>557</v>
       </c>
       <c r="B558" s="2" t="n">
         <v>45805</v>
@@ -15503,7 +15527,7 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>531</v>
+        <v>558</v>
       </c>
       <c r="B559" s="2" t="n">
         <v>45807</v>
@@ -15530,7 +15554,7 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>532</v>
+        <v>559</v>
       </c>
       <c r="B560" s="2" t="n">
         <v>45815</v>
@@ -15557,7 +15581,7 @@
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>533</v>
+        <v>560</v>
       </c>
       <c r="B561" s="2" t="n">
         <v>45818</v>
@@ -15584,7 +15608,7 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>534</v>
+        <v>561</v>
       </c>
       <c r="B562" s="2" t="n">
         <v>45818</v>
@@ -15611,7 +15635,7 @@
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>535</v>
+        <v>562</v>
       </c>
       <c r="B563" s="2" t="n">
         <v>45821</v>
@@ -15638,7 +15662,7 @@
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>536</v>
+        <v>563</v>
       </c>
       <c r="B564" s="2" t="n">
         <v>45828</v>
@@ -15665,7 +15689,7 @@
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>537</v>
+        <v>564</v>
       </c>
       <c r="B565" s="2" t="n">
         <v>45834</v>
@@ -15692,7 +15716,7 @@
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>538</v>
+        <v>565</v>
       </c>
       <c r="B566" s="2" t="n">
         <v>45836</v>
@@ -15719,7 +15743,7 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>523</v>
+        <v>566</v>
       </c>
       <c r="B567" s="2" t="n">
         <v>45838</v>
@@ -15746,7 +15770,7 @@
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>524</v>
+        <v>567</v>
       </c>
       <c r="B568" s="2" t="n">
         <v>45838</v>
@@ -15773,7 +15797,7 @@
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>525</v>
+        <v>568</v>
       </c>
       <c r="B569" s="2" t="n">
         <v>45838</v>
@@ -15800,7 +15824,7 @@
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>526</v>
+        <v>569</v>
       </c>
       <c r="B570" s="2" t="n">
         <v>45841</v>
@@ -15827,7 +15851,7 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>527</v>
+        <v>570</v>
       </c>
       <c r="B571" s="2" t="n">
         <v>45848</v>
@@ -15854,7 +15878,7 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>528</v>
+        <v>571</v>
       </c>
       <c r="B572" s="2" t="n">
         <v>45849</v>
@@ -15881,7 +15905,7 @@
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>529</v>
+        <v>572</v>
       </c>
       <c r="B573" s="2" t="n">
         <v>45849</v>
@@ -15908,7 +15932,7 @@
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>530</v>
+        <v>573</v>
       </c>
       <c r="B574" s="2" t="n">
         <v>45856</v>
@@ -15935,7 +15959,7 @@
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>531</v>
+        <v>574</v>
       </c>
       <c r="B575" s="2" t="n">
         <v>45857</v>
@@ -15962,7 +15986,7 @@
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>532</v>
+        <v>575</v>
       </c>
       <c r="B576" s="2" t="n">
         <v>45865</v>
@@ -15989,7 +16013,7 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>533</v>
+        <v>576</v>
       </c>
       <c r="B577" s="2" t="n">
         <v>45868</v>
@@ -16016,7 +16040,7 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>534</v>
+        <v>577</v>
       </c>
       <c r="B578" s="2" t="n">
         <v>45871</v>
@@ -16043,7 +16067,7 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>535</v>
+        <v>578</v>
       </c>
       <c r="B579" s="2" t="n">
         <v>45880</v>
@@ -16070,7 +16094,7 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>536</v>
+        <v>579</v>
       </c>
       <c r="B580" s="2" t="n">
         <v>45880</v>
@@ -16097,7 +16121,7 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>537</v>
+        <v>580</v>
       </c>
       <c r="B581" s="2" t="n">
         <v>45887</v>
@@ -16124,7 +16148,7 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>538</v>
+        <v>581</v>
       </c>
       <c r="B582" s="2" t="n">
         <v>45888</v>
@@ -16151,7 +16175,7 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>539</v>
+        <v>582</v>
       </c>
       <c r="B583" s="2" t="n">
         <v>45893</v>
@@ -16178,7 +16202,7 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>540</v>
+        <v>583</v>
       </c>
       <c r="B584" s="2" t="n">
         <v>45894</v>
@@ -16205,7 +16229,7 @@
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>541</v>
+        <v>584</v>
       </c>
       <c r="B585" s="2" t="n">
         <v>45896</v>
@@ -16232,7 +16256,7 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>542</v>
+        <v>585</v>
       </c>
       <c r="B586" s="2" t="n">
         <v>45898</v>
@@ -16259,7 +16283,7 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>543</v>
+        <v>586</v>
       </c>
       <c r="B587" s="2" t="n">
         <v>45899</v>
@@ -16286,7 +16310,7 @@
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>544</v>
+        <v>587</v>
       </c>
       <c r="B588" s="2" t="n">
         <v>45901</v>
@@ -16313,7 +16337,7 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>545</v>
+        <v>588</v>
       </c>
       <c r="B589" s="2" t="n">
         <v>45902</v>
@@ -16340,7 +16364,7 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>546</v>
+        <v>589</v>
       </c>
       <c r="B590" s="2" t="n">
         <v>45909</v>
@@ -16367,7 +16391,7 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>547</v>
+        <v>590</v>
       </c>
       <c r="B591" s="2" t="n">
         <v>45919</v>
@@ -16394,7 +16418,7 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>548</v>
+        <v>591</v>
       </c>
       <c r="B592" s="2" t="n">
         <v>45921</v>
@@ -16421,7 +16445,7 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>549</v>
+        <v>592</v>
       </c>
       <c r="B593" s="2" t="n">
         <v>45925</v>
@@ -16448,7 +16472,7 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>550</v>
+        <v>593</v>
       </c>
       <c r="B594" s="2" t="n">
         <v>45927</v>
@@ -16475,7 +16499,7 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>551</v>
+        <v>594</v>
       </c>
       <c r="B595" s="2" t="n">
         <v>45931</v>
@@ -16502,7 +16526,7 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>553</v>
+        <v>595</v>
       </c>
       <c r="B596" s="2" t="n">
         <v>45935</v>
@@ -16529,7 +16553,7 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>552</v>
+        <v>596</v>
       </c>
       <c r="B597" s="2" t="n">
         <v>45935</v>
@@ -16556,7 +16580,7 @@
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>554</v>
+        <v>597</v>
       </c>
       <c r="B598" s="2" t="n">
         <v>45940</v>
@@ -16583,7 +16607,7 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>555</v>
+        <v>598</v>
       </c>
       <c r="B599" s="2" t="n">
         <v>45955</v>
@@ -16610,7 +16634,7 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>556</v>
+        <v>599</v>
       </c>
       <c r="B600" s="2" t="n">
         <v>45960</v>
@@ -16637,7 +16661,7 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>557</v>
+        <v>600</v>
       </c>
       <c r="B601" s="2" t="n">
         <v>45961</v>
@@ -16664,7 +16688,7 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>558</v>
+        <v>601</v>
       </c>
       <c r="B602" s="2" t="n">
         <v>45961</v>
@@ -16691,7 +16715,7 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>559</v>
+        <v>602</v>
       </c>
       <c r="B603" s="2" t="n">
         <v>45968</v>
@@ -16718,7 +16742,7 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>560</v>
+        <v>603</v>
       </c>
       <c r="B604" s="2" t="n">
         <v>45968</v>
@@ -16745,7 +16769,7 @@
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>561</v>
+        <v>604</v>
       </c>
       <c r="B605" s="2" t="n">
         <v>45975</v>
@@ -16772,7 +16796,7 @@
     </row>
     <row r="606">
       <c r="A606" t="n">
-        <v>562</v>
+        <v>605</v>
       </c>
       <c r="B606" s="2" t="n">
         <v>45976</v>
@@ -16799,7 +16823,7 @@
     </row>
     <row r="607">
       <c r="A607" t="n">
-        <v>563</v>
+        <v>606</v>
       </c>
       <c r="B607" s="2" t="n">
         <v>45982</v>
@@ -16826,61 +16850,61 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>565</v>
+        <v>608</v>
       </c>
       <c r="B608" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeini Bulan November</t>
+          <t>Perekapan Kotak Amal 13 November</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E608" s="3" t="n">
-        <v>0</v>
+        <v>1992000</v>
       </c>
       <c r="F608" s="3" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G608" s="3" t="n">
-        <v>8028000</v>
+        <v>8528000</v>
       </c>
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>564</v>
+        <v>607</v>
       </c>
       <c r="B609" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Perekapan Kotak Amal 13 November</t>
+          <t>Gaji Bang Zaeini Bulan November</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E609" s="3" t="n">
-        <v>1992000</v>
+        <v>0</v>
       </c>
       <c r="F609" s="3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G609" s="3" t="n">
-        <v>8528000</v>
+        <v>8028000</v>
       </c>
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>566</v>
+        <v>609</v>
       </c>
       <c r="B610" s="2" t="n">
         <v>45992</v>
@@ -16907,7 +16931,7 @@
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>567</v>
+        <v>610</v>
       </c>
       <c r="B611" s="2" t="n">
         <v>46003</v>
@@ -16934,7 +16958,7 @@
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>568</v>
+        <v>611</v>
       </c>
       <c r="B612" s="2" t="n">
         <v>46013</v>
@@ -16961,7 +16985,7 @@
     </row>
     <row r="613">
       <c r="A613" t="n">
-        <v>569</v>
+        <v>612</v>
       </c>
       <c r="B613" s="2" t="n">
         <v>46014</v>
@@ -16988,7 +17012,7 @@
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>570</v>
+        <v>613</v>
       </c>
       <c r="B614" s="2" t="n">
         <v>46018</v>
@@ -17015,7 +17039,7 @@
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>571</v>
+        <v>614</v>
       </c>
       <c r="B615" s="2" t="n">
         <v>46019</v>
@@ -17042,7 +17066,7 @@
     </row>
     <row r="616">
       <c r="A616" t="n">
-        <v>572</v>
+        <v>615</v>
       </c>
       <c r="B616" s="2" t="n">
         <v>46021</v>
@@ -17069,7 +17093,7 @@
     </row>
     <row r="617">
       <c r="A617" t="n">
-        <v>573</v>
+        <v>616</v>
       </c>
       <c r="B617" s="2" t="n">
         <v>46031</v>
@@ -17096,7 +17120,7 @@
     </row>
     <row r="618">
       <c r="A618" t="n">
-        <v>574</v>
+        <v>617</v>
       </c>
       <c r="B618" s="2" t="n">
         <v>46032</v>
@@ -17123,7 +17147,7 @@
     </row>
     <row r="619">
       <c r="A619" t="n">
-        <v>575</v>
+        <v>618</v>
       </c>
       <c r="B619" s="2" t="n">
         <v>46038</v>
@@ -17150,7 +17174,7 @@
     </row>
     <row r="620">
       <c r="A620" t="n">
-        <v>576</v>
+        <v>619</v>
       </c>
       <c r="B620" s="2" t="n">
         <v>46042</v>
@@ -17177,7 +17201,7 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>577</v>
+        <v>620</v>
       </c>
       <c r="B621" s="2" t="n">
         <v>46047</v>
@@ -17204,7 +17228,7 @@
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>578</v>
+        <v>621</v>
       </c>
       <c r="B622" s="2" t="n">
         <v>46047</v>
@@ -17231,7 +17255,7 @@
     </row>
     <row r="623">
       <c r="A623" t="n">
-        <v>579</v>
+        <v>622</v>
       </c>
       <c r="B623" s="2" t="n">
         <v>46048</v>
@@ -17258,7 +17282,7 @@
     </row>
     <row r="624">
       <c r="A624" t="n">
-        <v>580</v>
+        <v>623</v>
       </c>
       <c r="B624" s="2" t="n">
         <v>46049</v>
@@ -17285,7 +17309,7 @@
     </row>
     <row r="625">
       <c r="A625" t="n">
-        <v>581</v>
+        <v>624</v>
       </c>
       <c r="B625" s="2" t="n">
         <v>46052</v>
@@ -17312,41 +17336,41 @@
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>584</v>
+        <v>628</v>
       </c>
       <c r="B626" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>Rekapan Infaq di rekening / QRIS</t>
+          <t>Realisasi Pengajuan Majelis Ta'lim</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Majelis Ta'lim</t>
         </is>
       </c>
       <c r="E626" s="3" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="F626" s="3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G626" s="3" t="n">
-        <v>5918600</v>
+        <v>5618600</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>585</v>
+        <v>627</v>
       </c>
       <c r="B627" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Januari 2026</t>
+          <t>Dana Kegiatan TPA Al Ikhlas</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -17361,66 +17385,66 @@
         <v>1200000</v>
       </c>
       <c r="G627" s="3" t="n">
-        <v>4718600</v>
+        <v>6118600</v>
       </c>
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>582</v>
+        <v>625</v>
       </c>
       <c r="B628" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Dana Kegiatan TPA Al Ikhlas</t>
+          <t>Rekapan Infaq di rekening / QRIS</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E628" s="3" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F628" s="3" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="G628" s="3" t="n">
-        <v>6118600</v>
+        <v>5918600</v>
       </c>
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>583</v>
+        <v>626</v>
       </c>
       <c r="B629" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Realisasi Pengajuan Majelis Ta'lim</t>
+          <t>Subsidi TPA Bulan Januari 2026</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
         <is>
-          <t>Majelis Ta'lim</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E629" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F629" s="3" t="n">
-        <v>500000</v>
+        <v>1200000</v>
       </c>
       <c r="G629" s="3" t="n">
-        <v>5618600</v>
+        <v>4718600</v>
       </c>
     </row>
     <row r="630">
       <c r="A630" t="n">
-        <v>586</v>
+        <v>629</v>
       </c>
       <c r="B630" s="2" t="n">
         <v>46056</v>
@@ -17447,7 +17471,7 @@
     </row>
     <row r="631">
       <c r="A631" t="n">
-        <v>587</v>
+        <v>630</v>
       </c>
       <c r="B631" s="2" t="n">
         <v>46057</v>
@@ -17474,7 +17498,7 @@
     </row>
     <row r="632">
       <c r="A632" t="n">
-        <v>588</v>
+        <v>631</v>
       </c>
       <c r="B632" s="2" t="n">
         <v>46062</v>
@@ -17501,7 +17525,7 @@
     </row>
     <row r="633">
       <c r="A633" t="n">
-        <v>589</v>
+        <v>632</v>
       </c>
       <c r="B633" s="2" t="n">
         <v>46066</v>
@@ -17528,7 +17552,7 @@
     </row>
     <row r="634">
       <c r="A634" t="n">
-        <v>590</v>
+        <v>633</v>
       </c>
       <c r="B634" s="2" t="n">
         <v>46067</v>
@@ -17555,7 +17579,7 @@
     </row>
     <row r="635">
       <c r="A635" t="n">
-        <v>591</v>
+        <v>634</v>
       </c>
       <c r="B635" s="2" t="n">
         <v>46071</v>
@@ -17582,7 +17606,7 @@
     </row>
     <row r="636">
       <c r="A636" t="n">
-        <v>592</v>
+        <v>635</v>
       </c>
       <c r="B636" s="2" t="n">
         <v>46072</v>
@@ -17609,7 +17633,7 @@
     </row>
     <row r="637">
       <c r="A637" t="n">
-        <v>593</v>
+        <v>636</v>
       </c>
       <c r="B637" s="2" t="n">
         <v>46073</v>
@@ -17636,7 +17660,7 @@
     </row>
     <row r="638">
       <c r="A638" t="n">
-        <v>594</v>
+        <v>637</v>
       </c>
       <c r="B638" s="2" t="n">
         <v>46073</v>
@@ -17663,61 +17687,61 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>596</v>
+        <v>639</v>
       </c>
       <c r="B639" s="2" t="n">
         <v>46074</v>
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Infaq Imam dan Ceramah Tarawih</t>
+          <t>Sumbangan Kantor Pak Jalal</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E639" s="3" t="n">
-        <v>0</v>
+        <v>10000000</v>
       </c>
       <c r="F639" s="3" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="G639" s="3" t="n">
-        <v>9818600</v>
+        <v>11318600</v>
       </c>
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>595</v>
+        <v>638</v>
       </c>
       <c r="B640" s="2" t="n">
         <v>46074</v>
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Sumbangan Kantor Pak Jalal</t>
+          <t>Infaq Imam dan Ceramah Tarawih</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E640" s="3" t="n">
-        <v>10000000</v>
+        <v>0</v>
       </c>
       <c r="F640" s="3" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="G640" s="3" t="n">
-        <v>11318600</v>
+        <v>9818600</v>
       </c>
     </row>
     <row r="641">
       <c r="A641" t="n">
-        <v>597</v>
+        <v>640</v>
       </c>
       <c r="B641" s="2" t="n">
         <v>46075</v>
@@ -17744,7 +17768,7 @@
     </row>
     <row r="642">
       <c r="A642" t="n">
-        <v>598</v>
+        <v>641</v>
       </c>
       <c r="B642" s="2" t="n">
         <v>46076</v>
@@ -17771,7 +17795,7 @@
     </row>
     <row r="643">
       <c r="A643" t="n">
-        <v>599</v>
+        <v>642</v>
       </c>
       <c r="B643" s="2" t="n">
         <v>46077</v>
@@ -17798,7 +17822,7 @@
     </row>
     <row r="644">
       <c r="A644" t="n">
-        <v>600</v>
+        <v>643</v>
       </c>
       <c r="B644" s="2" t="n">
         <v>46080</v>
@@ -17825,7 +17849,7 @@
     </row>
     <row r="645">
       <c r="A645" t="n">
-        <v>601</v>
+        <v>644</v>
       </c>
       <c r="B645" s="2" t="n">
         <v>46081</v>
@@ -17852,7 +17876,7 @@
     </row>
     <row r="646">
       <c r="A646" t="n">
-        <v>602</v>
+        <v>645</v>
       </c>
       <c r="B646" s="2" t="n">
         <v>46082</v>
@@ -17879,7 +17903,7 @@
     </row>
     <row r="647">
       <c r="A647" t="n">
-        <v>603</v>
+        <v>646</v>
       </c>
       <c r="B647" s="2" t="n">
         <v>46088</v>
@@ -17906,7 +17930,7 @@
     </row>
     <row r="648">
       <c r="A648" t="n">
-        <v>604</v>
+        <v>647</v>
       </c>
       <c r="B648" s="2" t="n">
         <v>46089</v>
@@ -17933,7 +17957,7 @@
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>605</v>
+        <v>648</v>
       </c>
       <c r="B649" s="2" t="n">
         <v>46090</v>
@@ -17960,7 +17984,7 @@
     </row>
     <row r="650">
       <c r="A650" t="n">
-        <v>606</v>
+        <v>649</v>
       </c>
       <c r="B650" s="2" t="n">
         <v>46093</v>
@@ -17987,7 +18011,7 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>608</v>
+        <v>650</v>
       </c>
       <c r="B651" s="2" t="n">
         <v>46094</v>
@@ -18014,7 +18038,7 @@
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>607</v>
+        <v>651</v>
       </c>
       <c r="B652" s="2" t="n">
         <v>46094</v>
@@ -18041,7 +18065,7 @@
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>609</v>
+        <v>652</v>
       </c>
       <c r="B653" s="2" t="n">
         <v>46096</v>
@@ -18068,7 +18092,7 @@
     </row>
     <row r="654">
       <c r="A654" t="n">
-        <v>610</v>
+        <v>653</v>
       </c>
       <c r="B654" s="2" t="n">
         <v>46100</v>
@@ -18095,7 +18119,7 @@
     </row>
     <row r="655">
       <c r="A655" t="n">
-        <v>611</v>
+        <v>654</v>
       </c>
       <c r="B655" s="2" t="n">
         <v>46106</v>
@@ -18122,7 +18146,7 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>612</v>
+        <v>655</v>
       </c>
       <c r="B656" s="2" t="n">
         <v>46110</v>
@@ -18149,7 +18173,7 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>613</v>
+        <v>656</v>
       </c>
       <c r="B657" s="2" t="n">
         <v>46118</v>
@@ -18176,7 +18200,7 @@
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>614</v>
+        <v>657</v>
       </c>
       <c r="B658" s="2" t="n">
         <v>46119</v>
@@ -18203,7 +18227,7 @@
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>615</v>
+        <v>658</v>
       </c>
       <c r="B659" s="2" t="n">
         <v>46125</v>
@@ -18230,14 +18254,14 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>616</v>
+        <v>660</v>
       </c>
       <c r="B660" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Halal Bihalal Warga 21 April 2026</t>
+          <t>buah untuk Ustadz Halal Bihalal Warga 21 April 2026</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -18249,22 +18273,22 @@
         <v>0</v>
       </c>
       <c r="F660" s="3" t="n">
-        <v>1500000</v>
+        <v>300000</v>
       </c>
       <c r="G660" s="3" t="n">
-        <v>10991600</v>
+        <v>10691600</v>
       </c>
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>617</v>
+        <v>659</v>
       </c>
       <c r="B661" s="2" t="n">
         <v>46133</v>
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>buah untuk Ustadz Halal Bihalal Warga 21 April 2026</t>
+          <t>Infaq Ustadz Halal Bihalal Warga 21 April 2026</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -18276,15 +18300,15 @@
         <v>0</v>
       </c>
       <c r="F661" s="3" t="n">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
       <c r="G661" s="3" t="n">
-        <v>10691600</v>
+        <v>10991600</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>619</v>
+        <v>661</v>
       </c>
       <c r="B662" s="2" t="n">
         <v>46137</v>
@@ -18311,7 +18335,7 @@
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>618</v>
+        <v>662</v>
       </c>
       <c r="B663" s="2" t="n">
         <v>46137</v>
@@ -18338,7 +18362,7 @@
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>620</v>
+        <v>663</v>
       </c>
       <c r="B664" s="2" t="n">
         <v>46138</v>
@@ -18365,7 +18389,7 @@
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>621</v>
+        <v>664</v>
       </c>
       <c r="B665" s="2" t="n">
         <v>46141</v>
@@ -18392,7 +18416,7 @@
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>622</v>
+        <v>665</v>
       </c>
       <c r="B666" s="2" t="n">
         <v>46144</v>
@@ -18419,7 +18443,7 @@
     </row>
     <row r="667">
       <c r="A667" t="n">
-        <v>623</v>
+        <v>666</v>
       </c>
       <c r="B667" s="2" t="n">
         <v>46151</v>
@@ -18446,7 +18470,7 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>624</v>
+        <v>667</v>
       </c>
       <c r="B668" s="2" t="n">
         <v>46168</v>
@@ -18473,7 +18497,7 @@
     </row>
     <row r="669">
       <c r="A669" t="n">
-        <v>625</v>
+        <v>668</v>
       </c>
       <c r="B669" s="2" t="n">
         <v>46171</v>
@@ -18500,61 +18524,61 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>627</v>
+        <v>670</v>
       </c>
       <c r="B670" s="2" t="n">
         <v>46172</v>
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Mei 2026</t>
+          <t>Tambahan Infaq Ustadz untuk acara remaja masjid</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E670" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F670" s="3" t="n">
-        <v>800000</v>
+        <v>300000</v>
       </c>
       <c r="G670" s="3" t="n">
-        <v>7091600</v>
+        <v>7891600</v>
       </c>
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>626</v>
+        <v>669</v>
       </c>
       <c r="B671" s="2" t="n">
         <v>46172</v>
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>Tambahan Infaq Ustadz untuk acara remaja masjid</t>
+          <t>Subsidi TPA Bulan Mei 2026</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E671" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F671" s="3" t="n">
-        <v>300000</v>
+        <v>800000</v>
       </c>
       <c r="G671" s="3" t="n">
-        <v>7891600</v>
+        <v>7091600</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>629</v>
+        <v>671</v>
       </c>
       <c r="B672" s="2" t="n">
         <v>46173</v>
@@ -18581,7 +18605,7 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>628</v>
+        <v>672</v>
       </c>
       <c r="B673" s="2" t="n">
         <v>46173</v>
@@ -18608,7 +18632,7 @@
     </row>
     <row r="674">
       <c r="A674" t="n">
-        <v>630</v>
+        <v>673</v>
       </c>
       <c r="B674" s="2" t="n">
         <v>46174</v>
@@ -18635,7 +18659,7 @@
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>631</v>
+        <v>674</v>
       </c>
       <c r="B675" s="2" t="n">
         <v>46194</v>
@@ -18662,7 +18686,7 @@
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>632</v>
+        <v>675</v>
       </c>
       <c r="B676" s="2" t="n">
         <v>46194</v>
@@ -18689,7 +18713,7 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>633</v>
+        <v>676</v>
       </c>
       <c r="B677" s="2" t="n">
         <v>46198</v>
@@ -18716,7 +18740,7 @@
     </row>
     <row r="678">
       <c r="A678" t="n">
-        <v>634</v>
+        <v>677</v>
       </c>
       <c r="B678" s="2" t="n">
         <v>46199</v>
@@ -18743,7 +18767,7 @@
     </row>
     <row r="679">
       <c r="A679" t="n">
-        <v>635</v>
+        <v>678</v>
       </c>
       <c r="B679" s="2" t="n">
         <v>46204</v>
@@ -18770,7 +18794,7 @@
     </row>
     <row r="680">
       <c r="A680" t="n">
-        <v>636</v>
+        <v>679</v>
       </c>
       <c r="B680" s="2" t="n">
         <v>46213</v>
@@ -18797,7 +18821,7 @@
     </row>
     <row r="681">
       <c r="A681" t="n">
-        <v>637</v>
+        <v>680</v>
       </c>
       <c r="B681" s="2" t="n">
         <v>46220</v>
@@ -18824,7 +18848,7 @@
     </row>
     <row r="682">
       <c r="A682" t="n">
-        <v>638</v>
+        <v>681</v>
       </c>
       <c r="B682" s="2" t="n">
         <v>46221</v>
@@ -18851,7 +18875,7 @@
     </row>
     <row r="683">
       <c r="A683" t="n">
-        <v>639</v>
+        <v>682</v>
       </c>
       <c r="B683" s="2" t="n">
         <v>46227</v>
@@ -18877,15 +18901,42 @@
       </c>
     </row>
     <row r="684">
-      <c r="C684" s="4" t="inlineStr">
+      <c r="A684" t="n">
+        <v>683</v>
+      </c>
+      <c r="B684" s="2" t="n">
+        <v>46228</v>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Pemasukan rekening/ qris</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Infaq Rekening/QRIS</t>
+        </is>
+      </c>
+      <c r="E684" s="3" t="n">
+        <v>569333</v>
+      </c>
+      <c r="F684" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G684" s="3" t="n">
+        <v>15711934</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="C685" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E684" s="5" t="n">
-        <v>377597311</v>
-      </c>
-      <c r="F684" s="5" t="n">
+      <c r="E685" s="5" t="n">
+        <v>378166644</v>
+      </c>
+      <c r="F685" s="5" t="n">
         <v>360617210</v>
       </c>
     </row>

--- a/data/laporan_keuangan.xlsx
+++ b/data/laporan_keuangan.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G685"/>
+  <dimension ref="A1:G686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1008,22 +1008,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Infaq Transport Ustadz Tarawih</t>
+          <t>Penyaluran dana ke Majelis Ta'lim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Majelis Ta'lim</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>400000</v>
+        <v>1200000</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>3229200</v>
+        <v>3979200</v>
       </c>
     </row>
     <row r="22">
@@ -1062,22 +1062,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Penyaluran dana ke Majelis Ta'lim</t>
+          <t>Infaq Transport Ustadz Tarawih</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Majelis Ta'lim</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1200000</v>
+        <v>400000</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3979200</v>
+        <v>3229200</v>
       </c>
     </row>
     <row r="24">
@@ -1872,22 +1872,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Penyaluran dana ke Majelis Ta'lim</t>
+          <t>Infaq Pembicara untuk acara Muharram</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Majelis Ta'lim</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>1756890</v>
+        <v>2956890</v>
       </c>
     </row>
     <row r="54">
@@ -1899,22 +1899,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Infaq Pembicara untuk acara Muharram</t>
+          <t>Penyaluran dana ke Majelis Ta'lim</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Majelis Ta'lim</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1500000</v>
+        <v>1200000</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>2956890</v>
+        <v>1756890</v>
       </c>
     </row>
     <row r="55">
@@ -2142,22 +2142,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Snack Anak2 untuk Acara Maulid</t>
+          <t>Sumbangan dari RT 1 untuk Acara Maulid</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Konsumsi &amp; Kegiatan</t>
+          <t>Kegiatan &amp; Sosial</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>3206890</v>
+        <v>4506890</v>
       </c>
     </row>
     <row r="64">
@@ -2196,22 +2196,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sumbangan dari RT 1 untuk Acara Maulid</t>
+          <t>Snack Anak2 untuk Acara Maulid</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kegiatan &amp; Sosial</t>
+          <t>Konsumsi &amp; Kegiatan</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
         <v>300000</v>
       </c>
-      <c r="F65" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G65" s="3" t="n">
-        <v>4506890</v>
+        <v>3206890</v>
       </c>
     </row>
     <row r="66">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Jalal</t>
+          <t>Infaq dari Pak Ridho</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2427,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>756890</v>
+        <v>606890</v>
       </c>
     </row>
     <row r="74">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Heri S</t>
+          <t>Infaq dari Pak Hardian</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2448,13 +2448,13 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="F74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>856890</v>
+        <v>656890</v>
       </c>
     </row>
     <row r="75">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Hardian</t>
+          <t>Infaq dari Pak Jalal</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2475,13 +2475,13 @@
         </is>
       </c>
       <c r="E75" s="3" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="F75" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>656890</v>
+        <v>756890</v>
       </c>
     </row>
     <row r="76">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Ridho</t>
+          <t>Infaq dari Pak Heri S</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2508,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>606890</v>
+        <v>856890</v>
       </c>
     </row>
     <row r="77">
@@ -3006,22 +3006,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Infaq ustadz Khotib Jum'at 6 Agustus 2020</t>
+          <t>Sisa Konsumsi Panitia</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Konsumsi &amp; Kegiatan</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>0</v>
+        <v>141000</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>7641890</v>
+        <v>8391890</v>
       </c>
     </row>
     <row r="96">
@@ -3033,22 +3033,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sisa Konsumsi Panitia</t>
+          <t>Infaq ustadz Khotib Jum'at 6 Agustus 2020</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Konsumsi &amp; Kegiatan</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>141000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>8391890</v>
+        <v>7641890</v>
       </c>
     </row>
     <row r="97">
@@ -3222,22 +3222,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Amal Bergerak</t>
+          <t>Infaq Ustadz Khotib Jum'at</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>2102000</v>
+        <v>0</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>7393890</v>
+        <v>5291890</v>
       </c>
     </row>
     <row r="104">
@@ -3249,22 +3249,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Khotib Jum'at</t>
+          <t>Pembukaan Kotak Amal Bergerak</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>0</v>
+        <v>2102000</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>5291890</v>
+        <v>7393890</v>
       </c>
     </row>
     <row r="105">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pembukaan Kencleng Masjid 23 Oktober 2020</t>
+          <t>Infaq Ustadz Khotib Jum'at</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>11243890</v>
+        <v>10893890</v>
       </c>
     </row>
     <row r="107">
@@ -3330,22 +3330,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Khotib Jum'at</t>
+          <t>Pembukaan Kencleng Masjid 23 Oktober 2020</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>10893890</v>
+        <v>11243890</v>
       </c>
     </row>
     <row r="108">
@@ -4464,22 +4464,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Material dan Jasa Renovasi Atap</t>
+          <t>Gaji Bang Zaeni April + THR</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Renovasi &amp; Aset Masjid</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E149" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>5971000</v>
+        <v>900000</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>9688290</v>
+        <v>15659290</v>
       </c>
     </row>
     <row r="150">
@@ -4491,22 +4491,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni April + THR</t>
+          <t>Material dan Jasa Renovasi Atap</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Renovasi &amp; Aset Masjid</t>
         </is>
       </c>
       <c r="E150" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>900000</v>
+        <v>5971000</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15659290</v>
+        <v>9688290</v>
       </c>
     </row>
     <row r="151">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Ceramah Tarawih</t>
+          <t>Beli Gorden Hijab</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E159" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>8754290</v>
+        <v>9754290</v>
       </c>
     </row>
     <row r="160">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Beli Gorden Hijab</t>
+          <t>Ceramah Tarawih</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>9754290</v>
+        <v>8754290</v>
       </c>
     </row>
     <row r="162">
@@ -6165,22 +6165,22 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Jasa Bersihin Karpet</t>
+          <t>Infaq Ustadz Sholat Jum'at</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Renovasi &amp; Aset Masjid</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E212" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F212" s="3" t="n">
-        <v>825000</v>
+        <v>300000</v>
       </c>
       <c r="G212" s="3" t="n">
-        <v>13575390</v>
+        <v>14400390</v>
       </c>
     </row>
     <row r="213">
@@ -6192,22 +6192,22 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Sholat Jum'at</t>
+          <t>Jasa Bersihin Karpet</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Renovasi &amp; Aset Masjid</t>
         </is>
       </c>
       <c r="E213" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F213" s="3" t="n">
-        <v>300000</v>
+        <v>825000</v>
       </c>
       <c r="G213" s="3" t="n">
-        <v>14400390</v>
+        <v>13575390</v>
       </c>
     </row>
     <row r="214">
@@ -9378,12 +9378,12 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Infaq Sholat Jum'at</t>
+          <t>Infaq Sholat Tarawih</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E331" s="3" t="n">
@@ -9393,7 +9393,7 @@
         <v>300000</v>
       </c>
       <c r="G331" s="3" t="n">
-        <v>10638390</v>
+        <v>10938390</v>
       </c>
     </row>
     <row r="332">
@@ -9405,12 +9405,12 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Infaq Sholat Tarawih</t>
+          <t>Infaq Sholat Jum'at</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E332" s="3" t="n">
@@ -9420,7 +9420,7 @@
         <v>300000</v>
       </c>
       <c r="G332" s="3" t="n">
-        <v>10938390</v>
+        <v>10638390</v>
       </c>
     </row>
     <row r="333">
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan April 2023</t>
+          <t>THR ke Babe Kus</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -9660,10 +9660,10 @@
         <v>0</v>
       </c>
       <c r="F341" s="3" t="n">
-        <v>600000</v>
+        <v>1000000</v>
       </c>
       <c r="G341" s="3" t="n">
-        <v>12049390</v>
+        <v>11049390</v>
       </c>
     </row>
     <row r="342">
@@ -9675,22 +9675,22 @@
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>THR ke Babe Kus</t>
+          <t>Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E342" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F342" s="3" t="n">
-        <v>1000000</v>
+        <v>300000</v>
       </c>
       <c r="G342" s="3" t="n">
-        <v>11049390</v>
+        <v>12649390</v>
       </c>
     </row>
     <row r="343">
@@ -9702,22 +9702,22 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Infaq Khotib Jum'at</t>
+          <t>Gaji Bang Zaeni Bulan April 2023</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E343" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F343" s="3" t="n">
-        <v>300000</v>
+        <v>600000</v>
       </c>
       <c r="G343" s="3" t="n">
-        <v>12649390</v>
+        <v>12049390</v>
       </c>
     </row>
     <row r="344">
@@ -9891,22 +9891,22 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Amal 18 Mei 2023</t>
+          <t>Infaq Pembicara Halal Bihalal</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E350" s="3" t="n">
-        <v>4267000</v>
+        <v>0</v>
       </c>
       <c r="F350" s="3" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="G350" s="3" t="n">
-        <v>14816390</v>
+        <v>13316390</v>
       </c>
     </row>
     <row r="351">
@@ -9918,22 +9918,22 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>Infaq Pembicara Halal Bihalal</t>
+          <t>Jasa Bongkar pasang tenda untuk 3 orang</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E351" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F351" s="3" t="n">
-        <v>1500000</v>
+        <v>600000</v>
       </c>
       <c r="G351" s="3" t="n">
-        <v>13316390</v>
+        <v>12716390</v>
       </c>
     </row>
     <row r="352">
@@ -9945,22 +9945,22 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Jasa Bongkar pasang tenda untuk 3 orang</t>
+          <t>Pembukaan Kotak Amal 18 Mei 2023</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E352" s="3" t="n">
-        <v>0</v>
+        <v>4267000</v>
       </c>
       <c r="F352" s="3" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="G352" s="3" t="n">
-        <v>12716390</v>
+        <v>14816390</v>
       </c>
     </row>
     <row r="353">
@@ -10215,22 +10215,22 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan Juni</t>
+          <t>Pembukaan Kotak Amal 25 Juni 2023</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E362" s="3" t="n">
-        <v>0</v>
+        <v>5572000</v>
       </c>
       <c r="F362" s="3" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="G362" s="3" t="n">
-        <v>13983890</v>
+        <v>14583890</v>
       </c>
     </row>
     <row r="363">
@@ -10242,22 +10242,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Amal 25 Juni 2023</t>
+          <t>Gaji Bang Zaeni Bulan Juni</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E363" s="3" t="n">
-        <v>5572000</v>
+        <v>0</v>
       </c>
       <c r="F363" s="3" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="G363" s="3" t="n">
-        <v>14583890</v>
+        <v>13983890</v>
       </c>
     </row>
     <row r="364">
@@ -12260,56 +12260,56 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B438" s="2" t="n">
         <v>45353</v>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Sumbangan Hamba Allah</t>
+          <t>Infaq untuk Ustadz Tarhib Ramadhan</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E438" s="3" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F438" s="3" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="G438" s="3" t="n">
-        <v>5119290</v>
+        <v>3619290</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B439" s="2" t="n">
         <v>45353</v>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Infaq untuk Ustadz Tarhib Ramadhan</t>
+          <t>Sumbangan Hamba Allah</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E439" s="3" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="F439" s="3" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="G439" s="3" t="n">
-        <v>3619290</v>
+        <v>5119290</v>
       </c>
     </row>
     <row r="440">
@@ -15149,56 +15149,56 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B545" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Reimburse Infaq Khotib Jum'at 25 April 2025</t>
+          <t>Pembelian Token Listrik</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Listrik &amp; Perawatan</t>
         </is>
       </c>
       <c r="E545" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F545" s="3" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="G545" s="3" t="n">
-        <v>5223000</v>
+        <v>4223000</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B546" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Pembelian Token Listrik</t>
+          <t>Reimburse Infaq Khotib Jum'at 25 April 2025</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Listrik &amp; Perawatan</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E546" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F546" s="3" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="G546" s="3" t="n">
-        <v>4223000</v>
+        <v>5223000</v>
       </c>
     </row>
     <row r="547">
@@ -15446,56 +15446,56 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B556" s="2" t="n">
         <v>45802</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan Mei</t>
+          <t>infaq dari Jamaah via transfer dan QRIS</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E556" s="3" t="n">
-        <v>0</v>
+        <v>1370500</v>
       </c>
       <c r="F556" s="3" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="G556" s="3" t="n">
-        <v>6577600</v>
+        <v>7948100</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B557" s="2" t="n">
         <v>45802</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>infaq dari Jamaah via transfer dan QRIS</t>
+          <t>Gaji Bang Zaeni Bulan Mei</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E557" s="3" t="n">
-        <v>1370500</v>
+        <v>0</v>
       </c>
       <c r="F557" s="3" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="G557" s="3" t="n">
-        <v>7948100</v>
+        <v>6577600</v>
       </c>
     </row>
     <row r="558">
@@ -15743,83 +15743,83 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B567" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Juni 2025</t>
+          <t>infaq dari Jamaah via transfer dan QRIS</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E567" s="3" t="n">
-        <v>0</v>
+        <v>255000</v>
       </c>
       <c r="F567" s="3" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="G567" s="3" t="n">
-        <v>4540100</v>
+        <v>6656100</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B568" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Setoran Pembukaan Kotak Amal 30 Juni 2025</t>
+          <t>Subsidi TPA Bulan Juni 2025</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E568" s="3" t="n">
-        <v>1861000</v>
+        <v>0</v>
       </c>
       <c r="F568" s="3" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="G568" s="3" t="n">
-        <v>6401100</v>
+        <v>4540100</v>
       </c>
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B569" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>infaq dari Jamaah via transfer dan QRIS</t>
+          <t>Setoran Pembukaan Kotak Amal 30 Juni 2025</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E569" s="3" t="n">
-        <v>255000</v>
+        <v>1861000</v>
       </c>
       <c r="F569" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G569" s="3" t="n">
-        <v>6656100</v>
+        <v>6401100</v>
       </c>
     </row>
     <row r="570">
@@ -16857,22 +16857,22 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Perekapan Kotak Amal 13 November</t>
+          <t>Gaji Bang Zaeini Bulan November</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E608" s="3" t="n">
-        <v>1992000</v>
+        <v>0</v>
       </c>
       <c r="F608" s="3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G608" s="3" t="n">
-        <v>8528000</v>
+        <v>8028000</v>
       </c>
     </row>
     <row r="609">
@@ -16884,22 +16884,22 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeini Bulan November</t>
+          <t>Perekapan Kotak Amal 13 November</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E609" s="3" t="n">
-        <v>0</v>
+        <v>1992000</v>
       </c>
       <c r="F609" s="3" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G609" s="3" t="n">
-        <v>8028000</v>
+        <v>8528000</v>
       </c>
     </row>
     <row r="610">
@@ -17336,7 +17336,7 @@
     </row>
     <row r="626">
       <c r="A626" t="n">
-        <v>628</v>
+        <v>625</v>
       </c>
       <c r="B626" s="2" t="n">
         <v>46053</v>
@@ -17363,7 +17363,7 @@
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B627" s="2" t="n">
         <v>46053</v>
@@ -17390,7 +17390,7 @@
     </row>
     <row r="628">
       <c r="A628" t="n">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B628" s="2" t="n">
         <v>46053</v>
@@ -17417,7 +17417,7 @@
     </row>
     <row r="629">
       <c r="A629" t="n">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B629" s="2" t="n">
         <v>46053</v>
@@ -17687,7 +17687,7 @@
     </row>
     <row r="639">
       <c r="A639" t="n">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B639" s="2" t="n">
         <v>46074</v>
@@ -17714,7 +17714,7 @@
     </row>
     <row r="640">
       <c r="A640" t="n">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B640" s="2" t="n">
         <v>46074</v>
@@ -18011,56 +18011,56 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B651" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>Rekapan Infaq di rekening / QRIS per 13 Maret 2026</t>
+          <t>Subsidi TPA Bulan Maret 2026</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E651" s="3" t="n">
-        <v>1982000</v>
+        <v>0</v>
       </c>
       <c r="F651" s="3" t="n">
-        <v>0</v>
+        <v>1100000</v>
       </c>
       <c r="G651" s="3" t="n">
-        <v>10878600</v>
+        <v>8896600</v>
       </c>
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B652" s="2" t="n">
         <v>46094</v>
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Maret 2026</t>
+          <t>Rekapan Infaq di rekening / QRIS per 13 Maret 2026</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E652" s="3" t="n">
-        <v>0</v>
+        <v>1982000</v>
       </c>
       <c r="F652" s="3" t="n">
-        <v>1100000</v>
+        <v>0</v>
       </c>
       <c r="G652" s="3" t="n">
-        <v>8896600</v>
+        <v>10878600</v>
       </c>
     </row>
     <row r="653">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>buah untuk Ustadz Halal Bihalal Warga 21 April 2026</t>
+          <t>Infaq Ustadz Halal Bihalal Warga 21 April 2026</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -18273,10 +18273,10 @@
         <v>0</v>
       </c>
       <c r="F660" s="3" t="n">
-        <v>300000</v>
+        <v>1500000</v>
       </c>
       <c r="G660" s="3" t="n">
-        <v>10691600</v>
+        <v>10991600</v>
       </c>
     </row>
     <row r="661">
@@ -18288,7 +18288,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Halal Bihalal Warga 21 April 2026</t>
+          <t>buah untuk Ustadz Halal Bihalal Warga 21 April 2026</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -18300,64 +18300,64 @@
         <v>0</v>
       </c>
       <c r="F661" s="3" t="n">
-        <v>1500000</v>
+        <v>300000</v>
       </c>
       <c r="G661" s="3" t="n">
-        <v>10991600</v>
+        <v>10691600</v>
       </c>
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B662" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeini Bulan April</t>
+          <t>Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E662" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F662" s="3" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="G662" s="3" t="n">
-        <v>9591600</v>
+        <v>10191600</v>
       </c>
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B663" s="2" t="n">
         <v>46137</v>
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Infaq Khotib Jum'at</t>
+          <t>Gaji Bang Zaeini Bulan April</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E663" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F663" s="3" t="n">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="G663" s="3" t="n">
-        <v>10191600</v>
+        <v>9591600</v>
       </c>
     </row>
     <row r="664">
@@ -18524,7 +18524,7 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B670" s="2" t="n">
         <v>46172</v>
@@ -18551,7 +18551,7 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="B671" s="2" t="n">
         <v>46172</v>
@@ -18578,56 +18578,56 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B672" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Rekapan Infaq di rekening / QRIS/</t>
+          <t>Penghitungan Kotak Amal 21 Mei 2026</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E672" s="3" t="n">
-        <v>4658001</v>
+        <v>2115000</v>
       </c>
       <c r="F672" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G672" s="3" t="n">
-        <v>13864601</v>
+        <v>9206600</v>
       </c>
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B673" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Penghitungan Kotak Amal 21 Mei 2026</t>
+          <t>Rekapan Infaq di rekening / QRIS/</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E673" s="3" t="n">
-        <v>2115000</v>
+        <v>4658001</v>
       </c>
       <c r="F673" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G673" s="3" t="n">
-        <v>9206600</v>
+        <v>13864601</v>
       </c>
     </row>
     <row r="674">
@@ -18928,15 +18928,42 @@
       </c>
     </row>
     <row r="685">
-      <c r="C685" s="4" t="inlineStr">
+      <c r="A685" t="n">
+        <v>684</v>
+      </c>
+      <c r="B685" s="2" t="n">
+        <v>46230</v>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Pemasukan Kotak Amal</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Kotak Amal / Kencleng</t>
+        </is>
+      </c>
+      <c r="E685" s="3" t="n">
+        <v>3108000</v>
+      </c>
+      <c r="F685" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G685" s="3" t="n">
+        <v>18819934</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="C686" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E685" s="5" t="n">
-        <v>378166644</v>
-      </c>
-      <c r="F685" s="5" t="n">
+      <c r="E686" s="5" t="n">
+        <v>381274644</v>
+      </c>
+      <c r="F686" s="5" t="n">
         <v>360617210</v>
       </c>
     </row>

--- a/data/laporan_keuangan.xlsx
+++ b/data/laporan_keuangan.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G686"/>
+  <dimension ref="A1:G687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1008,22 +1008,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Penyaluran dana ke Majelis Ta'lim</t>
+          <t>Infaq Transport Ustadz Tarawih</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Majelis Ta'lim</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>1200000</v>
+        <v>400000</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>3979200</v>
+        <v>3229200</v>
       </c>
     </row>
     <row r="22">
@@ -1062,22 +1062,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Infaq Transport Ustadz Tarawih</t>
+          <t>Penyaluran dana ke Majelis Ta'lim</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Majelis Ta'lim</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>400000</v>
+        <v>1200000</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3229200</v>
+        <v>3979200</v>
       </c>
     </row>
     <row r="24">
@@ -1872,22 +1872,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Infaq Pembicara untuk acara Muharram</t>
+          <t>Penyaluran dana ke Majelis Ta'lim</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Majelis Ta'lim</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1500000</v>
+        <v>1200000</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>2956890</v>
+        <v>1756890</v>
       </c>
     </row>
     <row r="54">
@@ -1899,22 +1899,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Penyaluran dana ke Majelis Ta'lim</t>
+          <t>Infaq Pembicara untuk acara Muharram</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Majelis Ta'lim</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>1756890</v>
+        <v>2956890</v>
       </c>
     </row>
     <row r="55">
@@ -2142,22 +2142,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Sumbangan dari RT 1 untuk Acara Maulid</t>
+          <t>Snack Anak2 untuk Acara Maulid</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Kegiatan &amp; Sosial</t>
+          <t>Konsumsi &amp; Kegiatan</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="3" t="n">
         <v>300000</v>
       </c>
-      <c r="F63" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G63" s="3" t="n">
-        <v>4506890</v>
+        <v>3206890</v>
       </c>
     </row>
     <row r="64">
@@ -2196,22 +2196,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Snack Anak2 untuk Acara Maulid</t>
+          <t>Sumbangan dari RT 1 untuk Acara Maulid</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Konsumsi &amp; Kegiatan</t>
+          <t>Kegiatan &amp; Sosial</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F65" s="3" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>3206890</v>
+        <v>4506890</v>
       </c>
     </row>
     <row r="66">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Ridho</t>
+          <t>Infaq dari Pak Heri S</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2427,7 +2427,7 @@
         <v>0</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>606890</v>
+        <v>856890</v>
       </c>
     </row>
     <row r="74">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Hardian</t>
+          <t>Infaq dari Pak Jalal</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2448,13 +2448,13 @@
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="F74" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>656890</v>
+        <v>756890</v>
       </c>
     </row>
     <row r="75">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Jalal</t>
+          <t>Infaq dari Pak Ridho</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>756890</v>
+        <v>606890</v>
       </c>
     </row>
     <row r="76">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Heri S</t>
+          <t>Infaq dari Pak Hardian</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="F76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>856890</v>
+        <v>656890</v>
       </c>
     </row>
     <row r="77">
@@ -3006,22 +3006,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Sisa Konsumsi Panitia</t>
+          <t>Infaq ustadz Khotib Jum'at 6 Agustus 2020</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Konsumsi &amp; Kegiatan</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>141000</v>
+        <v>0</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>8391890</v>
+        <v>7641890</v>
       </c>
     </row>
     <row r="96">
@@ -3033,22 +3033,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Infaq ustadz Khotib Jum'at 6 Agustus 2020</t>
+          <t>Sisa Konsumsi Panitia</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Konsumsi &amp; Kegiatan</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>0</v>
+        <v>141000</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>7641890</v>
+        <v>8391890</v>
       </c>
     </row>
     <row r="97">
@@ -3222,22 +3222,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Khotib Jum'at</t>
+          <t>Pembukaan Kotak Amal Bergerak</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>2102000</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>5291890</v>
+        <v>7393890</v>
       </c>
     </row>
     <row r="104">
@@ -3249,22 +3249,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Amal Bergerak</t>
+          <t>Infaq Ustadz Khotib Jum'at</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>2102000</v>
+        <v>0</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>7393890</v>
+        <v>5291890</v>
       </c>
     </row>
     <row r="105">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Khotib Jum'at</t>
+          <t>Pembukaan Kencleng Masjid 23 Oktober 2020</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>10893890</v>
+        <v>11243890</v>
       </c>
     </row>
     <row r="107">
@@ -3330,22 +3330,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Pembukaan Kencleng Masjid 23 Oktober 2020</t>
+          <t>Infaq Ustadz Khotib Jum'at</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>11243890</v>
+        <v>10893890</v>
       </c>
     </row>
     <row r="108">
@@ -4464,22 +4464,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni April + THR</t>
+          <t>Material dan Jasa Renovasi Atap</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Renovasi &amp; Aset Masjid</t>
         </is>
       </c>
       <c r="E149" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>900000</v>
+        <v>5971000</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>15659290</v>
+        <v>9688290</v>
       </c>
     </row>
     <row r="150">
@@ -4491,22 +4491,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Material dan Jasa Renovasi Atap</t>
+          <t>Gaji Bang Zaeni April + THR</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Renovasi &amp; Aset Masjid</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E150" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>5971000</v>
+        <v>900000</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>9688290</v>
+        <v>15659290</v>
       </c>
     </row>
     <row r="151">
@@ -4727,41 +4727,41 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B159" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Beli Gorden Hijab</t>
+          <t>Khotib Jum'at</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E159" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F159" s="3" t="n">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>9754290</v>
+        <v>9254290</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B160" s="2" t="n">
         <v>44323</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Khotib Jum'at</t>
+          <t>Ceramah Tarawih</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4776,7 +4776,7 @@
         <v>500000</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>9254290</v>
+        <v>8754290</v>
       </c>
     </row>
     <row r="161">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Ceramah Tarawih</t>
+          <t>Beli Gorden Hijab</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>8754290</v>
+        <v>9754290</v>
       </c>
     </row>
     <row r="162">
@@ -4997,56 +4997,56 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B169" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Khotib Jum'at</t>
+          <t>Gaji Bang Zaeni Bulan Mei 2021</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E169" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>500000</v>
+        <v>450000</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>11135490</v>
+        <v>10685490</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B170" s="2" t="n">
         <v>44344</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan Mei 2021</t>
+          <t>Khotib Jum'at</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E170" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>10685490</v>
+        <v>11135490</v>
       </c>
     </row>
     <row r="171">
@@ -6158,7 +6158,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B212" s="2" t="n">
         <v>44645</v>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B213" s="2" t="n">
         <v>44645</v>
@@ -6212,56 +6212,56 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B214" s="2" t="n">
         <v>44646</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Beli Perlengkapan (Mata Bor dan Lampu )</t>
+          <t>Infaq Ustadz Tarhib Ramadhan</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E214" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>500000</v>
+        <v>1500000</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>13075390</v>
+        <v>11575390</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B215" s="2" t="n">
         <v>44646</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Tarhib Ramadhan</t>
+          <t>Beli Perlengkapan (Mata Bor dan Lampu )</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E215" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>1500000</v>
+        <v>500000</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>11575390</v>
+        <v>13075390</v>
       </c>
     </row>
     <row r="216">
@@ -8804,41 +8804,41 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B310" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Transfer untuk Subsidi Kegiatan Sanlat TPA</t>
+          <t>Infaq Sholat Tarawih</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E310" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F310" s="3" t="n">
-        <v>850000</v>
+        <v>300000</v>
       </c>
       <c r="G310" s="3" t="n">
-        <v>10589390</v>
+        <v>10289390</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B311" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Infaq Sholat Tarawih</t>
+          <t>Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -8853,34 +8853,34 @@
         <v>300000</v>
       </c>
       <c r="G311" s="3" t="n">
-        <v>10289390</v>
+        <v>9989390</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B312" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Infaq Khotib Jum'at</t>
+          <t>Transfer untuk Subsidi Kegiatan Sanlat TPA</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E312" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F312" s="3" t="n">
-        <v>300000</v>
+        <v>850000</v>
       </c>
       <c r="G312" s="3" t="n">
-        <v>9989390</v>
+        <v>10589390</v>
       </c>
     </row>
     <row r="313">
@@ -9128,56 +9128,56 @@
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B322" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Infaq Sholat Tarawih</t>
+          <t>Pembukaan Kencleng 7 April 2023</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E322" s="3" t="n">
-        <v>0</v>
+        <v>3618000</v>
       </c>
       <c r="F322" s="3" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="G322" s="3" t="n">
-        <v>10420390</v>
+        <v>14038390</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B323" s="2" t="n">
         <v>45023</v>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Pembukaan Kencleng 7 April 2023</t>
+          <t>Infaq Sholat Tarawih</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E323" s="3" t="n">
-        <v>3618000</v>
+        <v>0</v>
       </c>
       <c r="F323" s="3" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>14038390</v>
+        <v>10420390</v>
       </c>
     </row>
     <row r="324">
@@ -9371,7 +9371,7 @@
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B331" s="2" t="n">
         <v>45030</v>
@@ -9398,7 +9398,7 @@
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B332" s="2" t="n">
         <v>45030</v>
@@ -9425,56 +9425,56 @@
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B333" s="2" t="n">
         <v>45032</v>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Infaq Sholat Tarawih</t>
+          <t>Pembukaan Kotak Amal 16 April</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E333" s="3" t="n">
-        <v>0</v>
+        <v>2531000</v>
       </c>
       <c r="F333" s="3" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G333" s="3" t="n">
-        <v>10338390</v>
+        <v>12869390</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B334" s="2" t="n">
         <v>45032</v>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Amal 16 April</t>
+          <t>Infaq Sholat Tarawih</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E334" s="3" t="n">
-        <v>2531000</v>
+        <v>0</v>
       </c>
       <c r="F334" s="3" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>12869390</v>
+        <v>10338390</v>
       </c>
     </row>
     <row r="335">
@@ -9641,7 +9641,7 @@
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B341" s="2" t="n">
         <v>45044</v>
@@ -9668,7 +9668,7 @@
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B342" s="2" t="n">
         <v>45044</v>
@@ -9695,7 +9695,7 @@
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B343" s="2" t="n">
         <v>45044</v>
@@ -9884,7 +9884,7 @@
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B350" s="2" t="n">
         <v>45064</v>
@@ -9911,7 +9911,7 @@
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B351" s="2" t="n">
         <v>45064</v>
@@ -9938,7 +9938,7 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B352" s="2" t="n">
         <v>45064</v>
@@ -9992,56 +9992,56 @@
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B354" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Infaq Khotib Jum'at</t>
+          <t>Gaji Bang Zaeni Bulan Mei</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E354" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F354" s="3" t="n">
-        <v>300000</v>
+        <v>600000</v>
       </c>
       <c r="G354" s="3" t="n">
-        <v>12116390</v>
+        <v>11516390</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B355" s="2" t="n">
         <v>45072</v>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan Mei</t>
+          <t>Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E355" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F355" s="3" t="n">
-        <v>600000</v>
+        <v>300000</v>
       </c>
       <c r="G355" s="3" t="n">
-        <v>11516390</v>
+        <v>12116390</v>
       </c>
     </row>
     <row r="356">
@@ -10208,7 +10208,7 @@
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B362" s="2" t="n">
         <v>45102</v>
@@ -10235,7 +10235,7 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B363" s="2" t="n">
         <v>45102</v>
@@ -10262,14 +10262,14 @@
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B364" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Pembelian Celengan Kaleng 100 buah</t>
+          <t>Pembayaran Spanduk Idul Adha</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -10281,22 +10281,22 @@
         <v>0</v>
       </c>
       <c r="F364" s="3" t="n">
-        <v>262600</v>
+        <v>60000</v>
       </c>
       <c r="G364" s="3" t="n">
-        <v>13721290</v>
+        <v>13661290</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B365" s="2" t="n">
         <v>45103</v>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Pembayaran Spanduk Idul Adha</t>
+          <t>Pembelian Celengan Kaleng 100 buah</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -10308,10 +10308,10 @@
         <v>0</v>
       </c>
       <c r="F365" s="3" t="n">
-        <v>60000</v>
+        <v>262600</v>
       </c>
       <c r="G365" s="3" t="n">
-        <v>13661290</v>
+        <v>13721290</v>
       </c>
     </row>
     <row r="366">
@@ -12267,22 +12267,22 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Infaq untuk Ustadz Tarhib Ramadhan</t>
+          <t>Sumbangan Hamba Allah</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E438" s="3" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="F438" s="3" t="n">
-        <v>1500000</v>
+        <v>0</v>
       </c>
       <c r="G438" s="3" t="n">
-        <v>3619290</v>
+        <v>5119290</v>
       </c>
     </row>
     <row r="439">
@@ -12294,22 +12294,22 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Sumbangan Hamba Allah</t>
+          <t>Infaq untuk Ustadz Tarhib Ramadhan</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E439" s="3" t="n">
-        <v>5000000</v>
+        <v>0</v>
       </c>
       <c r="F439" s="3" t="n">
-        <v>0</v>
+        <v>1500000</v>
       </c>
       <c r="G439" s="3" t="n">
-        <v>5119290</v>
+        <v>3619290</v>
       </c>
     </row>
     <row r="440">
@@ -15149,7 +15149,7 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B545" s="2" t="n">
         <v>45773</v>
@@ -15176,7 +15176,7 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B546" s="2" t="n">
         <v>45773</v>
@@ -15446,7 +15446,7 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B556" s="2" t="n">
         <v>45802</v>
@@ -15473,7 +15473,7 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B557" s="2" t="n">
         <v>45802</v>
@@ -15750,27 +15750,27 @@
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>infaq dari Jamaah via transfer dan QRIS</t>
+          <t>Setoran Pembukaan Kotak Amal 30 Juni 2025</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E567" s="3" t="n">
-        <v>255000</v>
+        <v>1861000</v>
       </c>
       <c r="F567" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G567" s="3" t="n">
-        <v>6656100</v>
+        <v>6401100</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B568" s="2" t="n">
         <v>45838</v>
@@ -15797,29 +15797,29 @@
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B569" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Setoran Pembukaan Kotak Amal 30 Juni 2025</t>
+          <t>infaq dari Jamaah via transfer dan QRIS</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E569" s="3" t="n">
-        <v>1861000</v>
+        <v>255000</v>
       </c>
       <c r="F569" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G569" s="3" t="n">
-        <v>6401100</v>
+        <v>6656100</v>
       </c>
     </row>
     <row r="570">
@@ -16067,56 +16067,56 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B579" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Reimburse Infaq Khotib Jum'at</t>
+          <t>infaq dari Jamaah via transfer dan QRIS</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E579" s="3" t="n">
-        <v>0</v>
+        <v>368000</v>
       </c>
       <c r="F579" s="3" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G579" s="3" t="n">
-        <v>5401100</v>
+        <v>5769100</v>
       </c>
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B580" s="2" t="n">
         <v>45880</v>
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>infaq dari Jamaah via transfer dan QRIS</t>
+          <t>Reimburse Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E580" s="3" t="n">
-        <v>368000</v>
+        <v>0</v>
       </c>
       <c r="F580" s="3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G580" s="3" t="n">
-        <v>5769100</v>
+        <v>5401100</v>
       </c>
     </row>
     <row r="581">
@@ -16661,56 +16661,56 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B601" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Infaq Khotib Jum'at</t>
+          <t>Subsidi TPA Bulan Oktober 2025</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E601" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F601" s="3" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="G601" s="3" t="n">
-        <v>7055000</v>
+        <v>6305000</v>
       </c>
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B602" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Oktober 2025</t>
+          <t>Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E602" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F602" s="3" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="G602" s="3" t="n">
-        <v>6305000</v>
+        <v>7055000</v>
       </c>
     </row>
     <row r="603">
@@ -16850,7 +16850,7 @@
     </row>
     <row r="608">
       <c r="A608" t="n">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B608" s="2" t="n">
         <v>45991</v>
@@ -16877,7 +16877,7 @@
     </row>
     <row r="609">
       <c r="A609" t="n">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B609" s="2" t="n">
         <v>45991</v>
@@ -18011,7 +18011,7 @@
     </row>
     <row r="651">
       <c r="A651" t="n">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="B651" s="2" t="n">
         <v>46094</v>
@@ -18038,7 +18038,7 @@
     </row>
     <row r="652">
       <c r="A652" t="n">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B652" s="2" t="n">
         <v>46094</v>
@@ -18254,7 +18254,7 @@
     </row>
     <row r="660">
       <c r="A660" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="B660" s="2" t="n">
         <v>46133</v>
@@ -18281,7 +18281,7 @@
     </row>
     <row r="661">
       <c r="A661" t="n">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B661" s="2" t="n">
         <v>46133</v>
@@ -18308,7 +18308,7 @@
     </row>
     <row r="662">
       <c r="A662" t="n">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B662" s="2" t="n">
         <v>46137</v>
@@ -18335,7 +18335,7 @@
     </row>
     <row r="663">
       <c r="A663" t="n">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B663" s="2" t="n">
         <v>46137</v>
@@ -18578,7 +18578,7 @@
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="B672" s="2" t="n">
         <v>46173</v>
@@ -18605,7 +18605,7 @@
     </row>
     <row r="673">
       <c r="A673" t="n">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="B673" s="2" t="n">
         <v>46173</v>
@@ -18659,56 +18659,56 @@
     </row>
     <row r="675">
       <c r="A675" t="n">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B675" s="2" t="n">
         <v>46194</v>
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Pemasukan dari rekening / qris</t>
+          <t>Penghitungan Kotak Amal 14 Juni 2026</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>966000</v>
+        <v>3712000</v>
       </c>
       <c r="F675" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G675" s="3" t="n">
-        <v>14330601</v>
+        <v>18042601</v>
       </c>
     </row>
     <row r="676">
       <c r="A676" t="n">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B676" s="2" t="n">
         <v>46194</v>
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Penghitungan Kotak Amal 14 Juni 2026</t>
+          <t>Pemasukan dari rekening / qris</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>3712000</v>
+        <v>966000</v>
       </c>
       <c r="F676" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G676" s="3" t="n">
-        <v>18042601</v>
+        <v>14330601</v>
       </c>
     </row>
     <row r="677">
@@ -18955,16 +18955,43 @@
       </c>
     </row>
     <row r="686">
-      <c r="C686" s="4" t="inlineStr">
+      <c r="A686" t="n">
+        <v>685</v>
+      </c>
+      <c r="B686" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Jasa Cuci Karpet</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Listrik &amp; Perawatan</t>
+        </is>
+      </c>
+      <c r="E686" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F686" s="3" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G686" s="3" t="n">
+        <v>18119934</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="C687" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E686" s="5" t="n">
+      <c r="E687" s="5" t="n">
         <v>381274644</v>
       </c>
-      <c r="F686" s="5" t="n">
-        <v>360617210</v>
+      <c r="F687" s="5" t="n">
+        <v>361317210</v>
       </c>
     </row>
   </sheetData>

--- a/data/laporan_keuangan.xlsx
+++ b/data/laporan_keuangan.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G687"/>
+  <dimension ref="A1:G688"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1008,22 +1008,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Infaq Transport Ustadz Tarawih</t>
+          <t>Penyaluran dana ke Majelis Ta'lim</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Majelis Ta'lim</t>
         </is>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="3" t="n">
-        <v>400000</v>
+        <v>1200000</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>3229200</v>
+        <v>3979200</v>
       </c>
     </row>
     <row r="22">
@@ -1062,22 +1062,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Penyaluran dana ke Majelis Ta'lim</t>
+          <t>Infaq Transport Ustadz Tarawih</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Majelis Ta'lim</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E23" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1200000</v>
+        <v>400000</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>3979200</v>
+        <v>3229200</v>
       </c>
     </row>
     <row r="24">
@@ -1872,22 +1872,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Penyaluran dana ke Majelis Ta'lim</t>
+          <t>Infaq Pembicara untuk acara Muharram</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Majelis Ta'lim</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E53" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="3" t="n">
-        <v>1200000</v>
+        <v>1500000</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>1756890</v>
+        <v>2956890</v>
       </c>
     </row>
     <row r="54">
@@ -1899,22 +1899,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Infaq Pembicara untuk acara Muharram</t>
+          <t>Penyaluran dana ke Majelis Ta'lim</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Majelis Ta'lim</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="3" t="n">
-        <v>1500000</v>
+        <v>1200000</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>2956890</v>
+        <v>1756890</v>
       </c>
     </row>
     <row r="55">
@@ -2142,22 +2142,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Snack Anak2 untuk Acara Maulid</t>
+          <t>Sumbangan dari RT 1 untuk Acara Maulid</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Konsumsi &amp; Kegiatan</t>
+          <t>Kegiatan &amp; Sosial</t>
         </is>
       </c>
       <c r="E63" s="3" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F63" s="3" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>3206890</v>
+        <v>4506890</v>
       </c>
     </row>
     <row r="64">
@@ -2196,22 +2196,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sumbangan dari RT 1 untuk Acara Maulid</t>
+          <t>Snack Anak2 untuk Acara Maulid</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Kegiatan &amp; Sosial</t>
+          <t>Konsumsi &amp; Kegiatan</t>
         </is>
       </c>
       <c r="E65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="3" t="n">
         <v>300000</v>
       </c>
-      <c r="F65" s="3" t="n">
-        <v>0</v>
-      </c>
       <c r="G65" s="3" t="n">
-        <v>4506890</v>
+        <v>3206890</v>
       </c>
     </row>
     <row r="66">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Heri S</t>
+          <t>Infaq dari Pak Hardian</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2421,13 +2421,13 @@
         </is>
       </c>
       <c r="E73" s="3" t="n">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="F73" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>856890</v>
+        <v>656890</v>
       </c>
     </row>
     <row r="74">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Jalal</t>
+          <t>Infaq dari Pak Ridho</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2454,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>756890</v>
+        <v>606890</v>
       </c>
     </row>
     <row r="75">
@@ -2466,7 +2466,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Ridho</t>
+          <t>Infaq dari Pak Heri S</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2481,7 +2481,7 @@
         <v>0</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>606890</v>
+        <v>856890</v>
       </c>
     </row>
     <row r="76">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Infaq dari Pak Hardian</t>
+          <t>Infaq dari Pak Jalal</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2502,13 +2502,13 @@
         </is>
       </c>
       <c r="E76" s="3" t="n">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="F76" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>656890</v>
+        <v>756890</v>
       </c>
     </row>
     <row r="77">
@@ -3006,22 +3006,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Infaq ustadz Khotib Jum'at 6 Agustus 2020</t>
+          <t>Sisa Konsumsi Panitia</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Konsumsi &amp; Kegiatan</t>
         </is>
       </c>
       <c r="E95" s="3" t="n">
-        <v>0</v>
+        <v>141000</v>
       </c>
       <c r="F95" s="3" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="G95" s="3" t="n">
-        <v>7641890</v>
+        <v>8391890</v>
       </c>
     </row>
     <row r="96">
@@ -3033,22 +3033,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Sisa Konsumsi Panitia</t>
+          <t>Infaq ustadz Khotib Jum'at 6 Agustus 2020</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Konsumsi &amp; Kegiatan</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E96" s="3" t="n">
-        <v>141000</v>
+        <v>0</v>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>8391890</v>
+        <v>7641890</v>
       </c>
     </row>
     <row r="97">
@@ -3222,22 +3222,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Amal Bergerak</t>
+          <t>Infaq Ustadz Khotib Jum'at</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E103" s="3" t="n">
-        <v>2102000</v>
+        <v>0</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>7393890</v>
+        <v>5291890</v>
       </c>
     </row>
     <row r="104">
@@ -3249,22 +3249,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Khotib Jum'at</t>
+          <t>Pembukaan Kotak Amal Bergerak</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E104" s="3" t="n">
-        <v>0</v>
+        <v>2102000</v>
       </c>
       <c r="F104" s="3" t="n">
-        <v>100000</v>
+        <v>0</v>
       </c>
       <c r="G104" s="3" t="n">
-        <v>5291890</v>
+        <v>7393890</v>
       </c>
     </row>
     <row r="105">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pembukaan Kencleng Masjid 23 Oktober 2020</t>
+          <t>Infaq Ustadz Khotib Jum'at</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E106" s="3" t="n">
-        <v>350000</v>
+        <v>0</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>11243890</v>
+        <v>10893890</v>
       </c>
     </row>
     <row r="107">
@@ -3330,22 +3330,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Khotib Jum'at</t>
+          <t>Pembukaan Kencleng Masjid 23 Oktober 2020</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E107" s="3" t="n">
-        <v>0</v>
+        <v>350000</v>
       </c>
       <c r="F107" s="3" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G107" s="3" t="n">
-        <v>10893890</v>
+        <v>11243890</v>
       </c>
     </row>
     <row r="108">
@@ -4464,22 +4464,22 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Material dan Jasa Renovasi Atap</t>
+          <t>Gaji Bang Zaeni April + THR</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Renovasi &amp; Aset Masjid</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E149" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F149" s="3" t="n">
-        <v>5971000</v>
+        <v>900000</v>
       </c>
       <c r="G149" s="3" t="n">
-        <v>9688290</v>
+        <v>15659290</v>
       </c>
     </row>
     <row r="150">
@@ -4491,22 +4491,22 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni April + THR</t>
+          <t>Material dan Jasa Renovasi Atap</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Renovasi &amp; Aset Masjid</t>
         </is>
       </c>
       <c r="E150" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F150" s="3" t="n">
-        <v>900000</v>
+        <v>5971000</v>
       </c>
       <c r="G150" s="3" t="n">
-        <v>15659290</v>
+        <v>9688290</v>
       </c>
     </row>
     <row r="151">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Khotib Jum'at</t>
+          <t>Ceramah Tarawih</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4749,7 +4749,7 @@
         <v>500000</v>
       </c>
       <c r="G159" s="3" t="n">
-        <v>9254290</v>
+        <v>8754290</v>
       </c>
     </row>
     <row r="160">
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Ceramah Tarawih</t>
+          <t>Beli Gorden Hijab</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E160" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F160" s="3" t="n">
-        <v>500000</v>
+        <v>800000</v>
       </c>
       <c r="G160" s="3" t="n">
-        <v>8754290</v>
+        <v>9754290</v>
       </c>
     </row>
     <row r="161">
@@ -4788,22 +4788,22 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Beli Gorden Hijab</t>
+          <t>Khotib Jum'at</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E161" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F161" s="3" t="n">
-        <v>800000</v>
+        <v>500000</v>
       </c>
       <c r="G161" s="3" t="n">
-        <v>9754290</v>
+        <v>9254290</v>
       </c>
     </row>
     <row r="162">
@@ -5004,22 +5004,22 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan Mei 2021</t>
+          <t>Khotib Jum'at</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E169" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F169" s="3" t="n">
-        <v>450000</v>
+        <v>500000</v>
       </c>
       <c r="G169" s="3" t="n">
-        <v>10685490</v>
+        <v>11135490</v>
       </c>
     </row>
     <row r="170">
@@ -5031,22 +5031,22 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Khotib Jum'at</t>
+          <t>Gaji Bang Zaeni Bulan Mei 2021</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E170" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F170" s="3" t="n">
-        <v>500000</v>
+        <v>450000</v>
       </c>
       <c r="G170" s="3" t="n">
-        <v>11135490</v>
+        <v>10685490</v>
       </c>
     </row>
     <row r="171">
@@ -6219,22 +6219,22 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Tarhib Ramadhan</t>
+          <t>Beli Perlengkapan (Mata Bor dan Lampu )</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E214" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F214" s="3" t="n">
-        <v>1500000</v>
+        <v>500000</v>
       </c>
       <c r="G214" s="3" t="n">
-        <v>11575390</v>
+        <v>13075390</v>
       </c>
     </row>
     <row r="215">
@@ -6246,22 +6246,22 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Beli Perlengkapan (Mata Bor dan Lampu )</t>
+          <t>Infaq Ustadz Tarhib Ramadhan</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E215" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F215" s="3" t="n">
-        <v>500000</v>
+        <v>1500000</v>
       </c>
       <c r="G215" s="3" t="n">
-        <v>13075390</v>
+        <v>11575390</v>
       </c>
     </row>
     <row r="216">
@@ -8811,7 +8811,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Infaq Sholat Tarawih</t>
+          <t>Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -8826,7 +8826,7 @@
         <v>300000</v>
       </c>
       <c r="G310" s="3" t="n">
-        <v>10289390</v>
+        <v>9989390</v>
       </c>
     </row>
     <row r="311">
@@ -8838,22 +8838,22 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Infaq Khotib Jum'at</t>
+          <t>Transfer untuk Subsidi Kegiatan Sanlat TPA</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E311" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F311" s="3" t="n">
-        <v>300000</v>
+        <v>850000</v>
       </c>
       <c r="G311" s="3" t="n">
-        <v>9989390</v>
+        <v>10589390</v>
       </c>
     </row>
     <row r="312">
@@ -8865,22 +8865,22 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Transfer untuk Subsidi Kegiatan Sanlat TPA</t>
+          <t>Infaq Sholat Tarawih</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E312" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F312" s="3" t="n">
-        <v>850000</v>
+        <v>300000</v>
       </c>
       <c r="G312" s="3" t="n">
-        <v>10589390</v>
+        <v>10289390</v>
       </c>
     </row>
     <row r="313">
@@ -9135,22 +9135,22 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Pembukaan Kencleng 7 April 2023</t>
+          <t>Infaq Sholat Tarawih</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E322" s="3" t="n">
-        <v>3618000</v>
+        <v>0</v>
       </c>
       <c r="F322" s="3" t="n">
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="G322" s="3" t="n">
-        <v>14038390</v>
+        <v>10420390</v>
       </c>
     </row>
     <row r="323">
@@ -9162,22 +9162,22 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Infaq Sholat Tarawih</t>
+          <t>Pembukaan Kencleng 7 April 2023</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E323" s="3" t="n">
-        <v>0</v>
+        <v>3618000</v>
       </c>
       <c r="F323" s="3" t="n">
-        <v>700000</v>
+        <v>0</v>
       </c>
       <c r="G323" s="3" t="n">
-        <v>10420390</v>
+        <v>14038390</v>
       </c>
     </row>
     <row r="324">
@@ -9432,22 +9432,22 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Amal 16 April</t>
+          <t>Infaq Sholat Tarawih</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E333" s="3" t="n">
-        <v>2531000</v>
+        <v>0</v>
       </c>
       <c r="F333" s="3" t="n">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="G333" s="3" t="n">
-        <v>12869390</v>
+        <v>10338390</v>
       </c>
     </row>
     <row r="334">
@@ -9459,22 +9459,22 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Infaq Sholat Tarawih</t>
+          <t>Pembukaan Kotak Amal 16 April</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E334" s="3" t="n">
-        <v>0</v>
+        <v>2531000</v>
       </c>
       <c r="F334" s="3" t="n">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="G334" s="3" t="n">
-        <v>10338390</v>
+        <v>12869390</v>
       </c>
     </row>
     <row r="335">
@@ -9999,22 +9999,22 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan Mei</t>
+          <t>Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E354" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F354" s="3" t="n">
-        <v>600000</v>
+        <v>300000</v>
       </c>
       <c r="G354" s="3" t="n">
-        <v>11516390</v>
+        <v>12116390</v>
       </c>
     </row>
     <row r="355">
@@ -10026,22 +10026,22 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Infaq Khotib Jum'at</t>
+          <t>Gaji Bang Zaeni Bulan Mei</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E355" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F355" s="3" t="n">
-        <v>300000</v>
+        <v>600000</v>
       </c>
       <c r="G355" s="3" t="n">
-        <v>12116390</v>
+        <v>11516390</v>
       </c>
     </row>
     <row r="356">
@@ -10269,7 +10269,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Pembayaran Spanduk Idul Adha</t>
+          <t>Pembelian Celengan Kaleng 100 buah</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
@@ -10281,10 +10281,10 @@
         <v>0</v>
       </c>
       <c r="F364" s="3" t="n">
-        <v>60000</v>
+        <v>262600</v>
       </c>
       <c r="G364" s="3" t="n">
-        <v>13661290</v>
+        <v>13721290</v>
       </c>
     </row>
     <row r="365">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Pembelian Celengan Kaleng 100 buah</t>
+          <t>Pembayaran Spanduk Idul Adha</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
@@ -10308,10 +10308,10 @@
         <v>0</v>
       </c>
       <c r="F365" s="3" t="n">
-        <v>262600</v>
+        <v>60000</v>
       </c>
       <c r="G365" s="3" t="n">
-        <v>13721290</v>
+        <v>13661290</v>
       </c>
     </row>
     <row r="366">
@@ -12260,7 +12260,7 @@
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B438" s="2" t="n">
         <v>45353</v>
@@ -12287,7 +12287,7 @@
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B439" s="2" t="n">
         <v>45353</v>
@@ -12314,56 +12314,56 @@
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B440" s="2" t="n">
         <v>45354</v>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Februari 2023</t>
+          <t>Sisa Dana Operasional Tarhib Ramadhan</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E440" s="3" t="n">
-        <v>0</v>
+        <v>739000</v>
       </c>
       <c r="F440" s="3" t="n">
-        <v>850000</v>
+        <v>0</v>
       </c>
       <c r="G440" s="3" t="n">
-        <v>2769290</v>
+        <v>3508290</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B441" s="2" t="n">
         <v>45354</v>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Sisa Dana Operasional Tarhib Ramadhan</t>
+          <t>Subsidi TPA Bulan Februari 2023</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E441" s="3" t="n">
-        <v>739000</v>
+        <v>0</v>
       </c>
       <c r="F441" s="3" t="n">
-        <v>0</v>
+        <v>850000</v>
       </c>
       <c r="G441" s="3" t="n">
-        <v>3508290</v>
+        <v>2769290</v>
       </c>
     </row>
     <row r="442">
@@ -13475,56 +13475,56 @@
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B483" s="2" t="n">
         <v>45556</v>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Hadiah Lomba Acara Maulid Nabi Muhammad SAW</t>
+          <t>Transport Ustadz Kajian Umum</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
         <is>
-          <t>Kegiatan &amp; Sosial</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E483" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F483" s="3" t="n">
-        <v>2000000</v>
+        <v>1500000</v>
       </c>
       <c r="G483" s="3" t="n">
-        <v>6433290</v>
+        <v>4933290</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B484" s="2" t="n">
         <v>45556</v>
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Transport Ustadz Kajian Umum</t>
+          <t>Hadiah Lomba Acara Maulid Nabi Muhammad SAW</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Kegiatan &amp; Sosial</t>
         </is>
       </c>
       <c r="E484" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F484" s="3" t="n">
-        <v>1500000</v>
+        <v>2000000</v>
       </c>
       <c r="G484" s="3" t="n">
-        <v>4933290</v>
+        <v>6433290</v>
       </c>
     </row>
     <row r="485">
@@ -13772,56 +13772,56 @@
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="B494" s="2" t="n">
         <v>45591</v>
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaini Bulan Oktober 2024</t>
+          <t>Pembukaan Kotak Amal</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E494" s="3" t="n">
-        <v>0</v>
+        <v>1002000</v>
       </c>
       <c r="F494" s="3" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="G494" s="3" t="n">
-        <v>2123290</v>
+        <v>3125290</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B495" s="2" t="n">
         <v>45591</v>
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Amal</t>
+          <t>Gaji Bang Zaini Bulan Oktober 2024</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E495" s="3" t="n">
-        <v>1002000</v>
+        <v>0</v>
       </c>
       <c r="F495" s="3" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="G495" s="3" t="n">
-        <v>3125290</v>
+        <v>2123290</v>
       </c>
     </row>
     <row r="496">
@@ -14366,56 +14366,56 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B516" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Akomodasi ustadzah Majelis Ta'lim</t>
+          <t>Donasi pak Yeni Rahman</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Majelis Ta'lim</t>
+          <t>Lainnya</t>
         </is>
       </c>
       <c r="E516" s="3" t="n">
-        <v>0</v>
+        <v>150000</v>
       </c>
       <c r="F516" s="3" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G516" s="3" t="n">
-        <v>1710290</v>
+        <v>1860290</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B517" s="2" t="n">
         <v>45696</v>
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Donasi pak Yeni Rahman</t>
+          <t>Akomodasi ustadzah Majelis Ta'lim</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Lainnya</t>
+          <t>Majelis Ta'lim</t>
         </is>
       </c>
       <c r="E517" s="3" t="n">
-        <v>150000</v>
+        <v>0</v>
       </c>
       <c r="F517" s="3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G517" s="3" t="n">
-        <v>1860290</v>
+        <v>1710290</v>
       </c>
     </row>
     <row r="518">
@@ -14663,56 +14663,56 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B527" s="2" t="n">
         <v>45724</v>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Infaq Ustadz Sholat Tarawih, 8 Maret 2025</t>
+          <t>Pembukaan Kotak Infaq 8 Maret 2025</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Infaq &amp; Sumbangan Lain</t>
         </is>
       </c>
       <c r="E527" s="3" t="n">
-        <v>0</v>
+        <v>1920000</v>
       </c>
       <c r="F527" s="3" t="n">
-        <v>750000</v>
+        <v>0</v>
       </c>
       <c r="G527" s="3" t="n">
-        <v>120290</v>
+        <v>2040290</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B528" s="2" t="n">
         <v>45724</v>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Pembukaan Kotak Infaq 8 Maret 2025</t>
+          <t>Infaq Ustadz Sholat Tarawih, 8 Maret 2025</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Infaq &amp; Sumbangan Lain</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E528" s="3" t="n">
-        <v>1920000</v>
+        <v>0</v>
       </c>
       <c r="F528" s="3" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="G528" s="3" t="n">
-        <v>2040290</v>
+        <v>120290</v>
       </c>
     </row>
     <row r="529">
@@ -14933,14 +14933,14 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B537" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Kotak Amal 26 Maret 2026</t>
+          <t>Penukaran Receh Kotak Amal 26 Maret</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -14949,25 +14949,25 @@
         </is>
       </c>
       <c r="E537" s="3" t="n">
-        <v>2005000</v>
+        <v>50000</v>
       </c>
       <c r="F537" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G537" s="3" t="n">
-        <v>4252000</v>
+        <v>4302000</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B538" s="2" t="n">
         <v>45742</v>
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Penukaran Receh Kotak Amal 26 Maret</t>
+          <t>Kotak Amal 26 Maret 2026</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -14976,13 +14976,13 @@
         </is>
       </c>
       <c r="E538" s="3" t="n">
-        <v>50000</v>
+        <v>2005000</v>
       </c>
       <c r="F538" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G538" s="3" t="n">
-        <v>4302000</v>
+        <v>4252000</v>
       </c>
     </row>
     <row r="539">
@@ -15149,56 +15149,56 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B545" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Pembelian Token Listrik</t>
+          <t>Reimburse Infaq Khotib Jum'at 25 April 2025</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
         <is>
-          <t>Listrik &amp; Perawatan</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E545" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F545" s="3" t="n">
-        <v>1000000</v>
+        <v>500000</v>
       </c>
       <c r="G545" s="3" t="n">
-        <v>4223000</v>
+        <v>5223000</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B546" s="2" t="n">
         <v>45773</v>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Reimburse Infaq Khotib Jum'at 25 April 2025</t>
+          <t>Pembelian Token Listrik</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Listrik &amp; Perawatan</t>
         </is>
       </c>
       <c r="E546" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F546" s="3" t="n">
-        <v>500000</v>
+        <v>1000000</v>
       </c>
       <c r="G546" s="3" t="n">
-        <v>5223000</v>
+        <v>4223000</v>
       </c>
     </row>
     <row r="547">
@@ -15446,56 +15446,56 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B556" s="2" t="n">
         <v>45802</v>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>infaq dari Jamaah via transfer dan QRIS</t>
+          <t>Gaji Bang Zaeni Bulan Mei</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E556" s="3" t="n">
-        <v>1370500</v>
+        <v>0</v>
       </c>
       <c r="F556" s="3" t="n">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="G556" s="3" t="n">
-        <v>7948100</v>
+        <v>6577600</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B557" s="2" t="n">
         <v>45802</v>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaeni Bulan Mei</t>
+          <t>infaq dari Jamaah via transfer dan QRIS</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E557" s="3" t="n">
-        <v>0</v>
+        <v>1370500</v>
       </c>
       <c r="F557" s="3" t="n">
-        <v>600000</v>
+        <v>0</v>
       </c>
       <c r="G557" s="3" t="n">
-        <v>6577600</v>
+        <v>7948100</v>
       </c>
     </row>
     <row r="558">
@@ -15743,56 +15743,56 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B567" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Setoran Pembukaan Kotak Amal 30 Juni 2025</t>
+          <t>Subsidi TPA Bulan Juni 2025</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E567" s="3" t="n">
-        <v>1861000</v>
+        <v>0</v>
       </c>
       <c r="F567" s="3" t="n">
-        <v>0</v>
+        <v>1200000</v>
       </c>
       <c r="G567" s="3" t="n">
-        <v>6401100</v>
+        <v>4540100</v>
       </c>
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B568" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Juni 2025</t>
+          <t>infaq dari Jamaah via transfer dan QRIS</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E568" s="3" t="n">
-        <v>0</v>
+        <v>255000</v>
       </c>
       <c r="F568" s="3" t="n">
-        <v>1200000</v>
+        <v>0</v>
       </c>
       <c r="G568" s="3" t="n">
-        <v>4540100</v>
+        <v>6656100</v>
       </c>
     </row>
     <row r="569">
@@ -15804,22 +15804,22 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>infaq dari Jamaah via transfer dan QRIS</t>
+          <t>Setoran Pembukaan Kotak Amal 30 Juni 2025</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E569" s="3" t="n">
-        <v>255000</v>
+        <v>1861000</v>
       </c>
       <c r="F569" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G569" s="3" t="n">
-        <v>6656100</v>
+        <v>6401100</v>
       </c>
     </row>
     <row r="570">
@@ -16074,22 +16074,22 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>infaq dari Jamaah via transfer dan QRIS</t>
+          <t>Reimburse Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E579" s="3" t="n">
-        <v>368000</v>
+        <v>0</v>
       </c>
       <c r="F579" s="3" t="n">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="G579" s="3" t="n">
-        <v>5769100</v>
+        <v>5401100</v>
       </c>
     </row>
     <row r="580">
@@ -16101,22 +16101,22 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Reimburse Infaq Khotib Jum'at</t>
+          <t>infaq dari Jamaah via transfer dan QRIS</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E580" s="3" t="n">
-        <v>0</v>
+        <v>368000</v>
       </c>
       <c r="F580" s="3" t="n">
-        <v>500000</v>
+        <v>0</v>
       </c>
       <c r="G580" s="3" t="n">
-        <v>5401100</v>
+        <v>5769100</v>
       </c>
     </row>
     <row r="581">
@@ -16668,22 +16668,22 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Subsidi TPA Bulan Oktober 2025</t>
+          <t>Infaq Khotib Jum'at</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>TPA</t>
+          <t>Infaq Ustadz/Khotib/Imam</t>
         </is>
       </c>
       <c r="E601" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F601" s="3" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="G601" s="3" t="n">
-        <v>6305000</v>
+        <v>7055000</v>
       </c>
     </row>
     <row r="602">
@@ -16695,22 +16695,22 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Infaq Khotib Jum'at</t>
+          <t>Subsidi TPA Bulan Oktober 2025</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
         <is>
-          <t>Infaq Ustadz/Khotib/Imam</t>
+          <t>TPA</t>
         </is>
       </c>
       <c r="E602" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F602" s="3" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="G602" s="3" t="n">
-        <v>7055000</v>
+        <v>6305000</v>
       </c>
     </row>
     <row r="603">
@@ -17201,56 +17201,56 @@
     </row>
     <row r="621">
       <c r="A621" t="n">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B621" s="2" t="n">
         <v>46047</v>
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Gaji Bang Zaini Bulan Januari</t>
+          <t>Konsumsi Rapat DKM</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
         <is>
-          <t>Gaji Marbot / Staf</t>
+          <t>Konsumsi &amp; Kegiatan</t>
         </is>
       </c>
       <c r="E621" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F621" s="3" t="n">
-        <v>600000</v>
+        <v>200000</v>
       </c>
       <c r="G621" s="3" t="n">
-        <v>9228600</v>
+        <v>9028600</v>
       </c>
     </row>
     <row r="622">
       <c r="A622" t="n">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B622" s="2" t="n">
         <v>46047</v>
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Konsumsi Rapat DKM</t>
+          <t>Gaji Bang Zaini Bulan Januari</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
         <is>
-          <t>Konsumsi &amp; Kegiatan</t>
+          <t>Gaji Marbot / Staf</t>
         </is>
       </c>
       <c r="E622" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F622" s="3" t="n">
-        <v>200000</v>
+        <v>600000</v>
       </c>
       <c r="G622" s="3" t="n">
-        <v>9028600</v>
+        <v>9228600</v>
       </c>
     </row>
     <row r="623">
@@ -18666,22 +18666,22 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Penghitungan Kotak Amal 14 Juni 2026</t>
+          <t>Pemasukan dari rekening / qris</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
         <is>
-          <t>Kotak Amal / Kencleng</t>
+          <t>Infaq Rekening/QRIS</t>
         </is>
       </c>
       <c r="E675" s="3" t="n">
-        <v>3712000</v>
+        <v>966000</v>
       </c>
       <c r="F675" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G675" s="3" t="n">
-        <v>18042601</v>
+        <v>14330601</v>
       </c>
     </row>
     <row r="676">
@@ -18693,22 +18693,22 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>Pemasukan dari rekening / qris</t>
+          <t>Penghitungan Kotak Amal 14 Juni 2026</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
         <is>
-          <t>Infaq Rekening/QRIS</t>
+          <t>Kotak Amal / Kencleng</t>
         </is>
       </c>
       <c r="E676" s="3" t="n">
-        <v>966000</v>
+        <v>3712000</v>
       </c>
       <c r="F676" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G676" s="3" t="n">
-        <v>14330601</v>
+        <v>18042601</v>
       </c>
     </row>
     <row r="677">
@@ -18982,16 +18982,43 @@
       </c>
     </row>
     <row r="687">
-      <c r="C687" s="4" t="inlineStr">
+      <c r="A687" t="n">
+        <v>686</v>
+      </c>
+      <c r="B687" s="2" t="n">
+        <v>46231</v>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Jasa Cuci / Perawatan AC lt Bawah ( 4</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Listrik &amp; Perawatan</t>
+        </is>
+      </c>
+      <c r="E687" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F687" s="3" t="n">
+        <v>340000</v>
+      </c>
+      <c r="G687" s="3" t="n">
+        <v>17779934</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="C688" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="E687" s="5" t="n">
+      <c r="E688" s="5" t="n">
         <v>381274644</v>
       </c>
-      <c r="F687" s="5" t="n">
-        <v>361317210</v>
+      <c r="F688" s="5" t="n">
+        <v>361657210</v>
       </c>
     </row>
   </sheetData>
